--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_publishing_newspapers.xlsx
@@ -1261,7 +1261,7 @@
         <v>1.7109692396982</v>
       </c>
       <c r="H2">
-        <v>3.57208357515961</v>
+        <v>3.5720835751596</v>
       </c>
       <c r="I2">
         <v>0.0478983541033682</v>
@@ -1291,7 +1291,7 @@
         <v>0.0957378256114934</v>
       </c>
       <c r="R2">
-        <v>0.0949052691789708</v>
+        <v>0.0949052691789707</v>
       </c>
       <c r="S2">
         <v>0.0489892933300273</v>
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09606660120303138</v>
+        <v>0.09591046800062532</v>
       </c>
       <c r="C2">
-        <v>6115.581758248823</v>
+        <v>6072.547732435803</v>
       </c>
       <c r="D2">
-        <v>5941.681758248823</v>
+        <v>5960.194732435803</v>
       </c>
       <c r="E2">
-        <v>-294.8</v>
+        <v>-233.253</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>61.547</v>
       </c>
       <c r="G2">
         <v>173.9</v>
@@ -1573,28 +1573,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.0958141</v>
       </c>
       <c r="N2">
-        <v>109.0163265306122</v>
+        <v>105.9205124306122</v>
       </c>
       <c r="O2">
-        <v>21.80326530612245</v>
+        <v>21.18410248612245</v>
       </c>
       <c r="P2">
-        <v>87.21306122448979</v>
+        <v>84.73640994448979</v>
       </c>
       <c r="Q2">
-        <v>154.0130612244898</v>
+        <v>151.5364099444898</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09606660120303138</v>
+        <v>0.09647279596022759</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226995</v>
+        <v>0.9877071104903578</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>35.21410621219545</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09591046800062532</v>
+        <v>0.09575433479821924</v>
       </c>
       <c r="C3">
-        <v>6072.547732435803</v>
+        <v>6029.629431912995</v>
       </c>
       <c r="D3">
-        <v>5960.194732435803</v>
+        <v>5978.823431912995</v>
       </c>
       <c r="E3">
-        <v>-233.253</v>
+        <v>-171.706</v>
       </c>
       <c r="F3">
-        <v>61.547</v>
+        <v>123.094</v>
       </c>
       <c r="G3">
         <v>173.9</v>
@@ -1655,28 +1655,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M3">
-        <v>3.0958141</v>
+        <v>6.191628199999999</v>
       </c>
       <c r="N3">
-        <v>105.9205124306122</v>
+        <v>102.8246983306123</v>
       </c>
       <c r="O3">
-        <v>21.18410248612245</v>
+        <v>20.56493966612245</v>
       </c>
       <c r="P3">
-        <v>84.73640994448979</v>
+        <v>82.25975866448979</v>
       </c>
       <c r="Q3">
-        <v>151.5364099444898</v>
+        <v>149.0597586644898</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09647279596022759</v>
+        <v>0.09688728040634617</v>
       </c>
       <c r="T3">
-        <v>0.9877071104903578</v>
+        <v>0.9957861838247027</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>35.21410621219545</v>
+        <v>17.60705310609772</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09575433479821924</v>
+        <v>0.09559820159581318</v>
       </c>
       <c r="C4">
-        <v>6029.629431912995</v>
+        <v>5986.827945187182</v>
       </c>
       <c r="D4">
-        <v>5978.823431912995</v>
+        <v>5997.568945187182</v>
       </c>
       <c r="E4">
-        <v>-171.706</v>
+        <v>-110.159</v>
       </c>
       <c r="F4">
-        <v>123.094</v>
+        <v>184.641</v>
       </c>
       <c r="G4">
         <v>173.9</v>
@@ -1737,28 +1737,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M4">
-        <v>6.191628199999999</v>
+        <v>9.287442299999999</v>
       </c>
       <c r="N4">
-        <v>102.8246983306123</v>
+        <v>99.72888423061225</v>
       </c>
       <c r="O4">
-        <v>20.56493966612245</v>
+        <v>19.94577684612245</v>
       </c>
       <c r="P4">
-        <v>82.25975866448979</v>
+        <v>79.7831073844898</v>
       </c>
       <c r="Q4">
-        <v>149.0597586644898</v>
+        <v>146.5831073844898</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09688728040634617</v>
+        <v>0.09731031092351874</v>
       </c>
       <c r="T4">
-        <v>0.9957861838247027</v>
+        <v>1.004031835990684</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>17.60705310609772</v>
+        <v>11.73803540406515</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09559820159581318</v>
+        <v>0.09544206839340713</v>
       </c>
       <c r="C5">
-        <v>5986.827945187182</v>
+        <v>5944.144374459348</v>
       </c>
       <c r="D5">
-        <v>5997.568945187182</v>
+        <v>6016.432374459348</v>
       </c>
       <c r="E5">
-        <v>-110.159</v>
+        <v>-48.61200000000002</v>
       </c>
       <c r="F5">
-        <v>184.641</v>
+        <v>246.188</v>
       </c>
       <c r="G5">
         <v>173.9</v>
@@ -1819,28 +1819,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M5">
-        <v>9.287442299999999</v>
+        <v>12.3832564</v>
       </c>
       <c r="N5">
-        <v>99.72888423061225</v>
+        <v>96.63307013061225</v>
       </c>
       <c r="O5">
-        <v>19.94577684612245</v>
+        <v>19.32661402612245</v>
       </c>
       <c r="P5">
-        <v>79.7831073844898</v>
+        <v>77.3064561044898</v>
       </c>
       <c r="Q5">
-        <v>146.5831073844898</v>
+        <v>144.1064561044898</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09731031092351874</v>
+        <v>0.09774215457646576</v>
       </c>
       <c r="T5">
-        <v>1.004031835990684</v>
+        <v>1.01244927257679</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>11.73803540406515</v>
+        <v>8.803526553048862</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09544206839340713</v>
+        <v>0.09534593519100107</v>
       </c>
       <c r="C6">
-        <v>5944.144374459348</v>
+        <v>5894.270964007848</v>
       </c>
       <c r="D6">
-        <v>6016.432374459348</v>
+        <v>6028.105964007848</v>
       </c>
       <c r="E6">
-        <v>-48.61200000000002</v>
+        <v>12.935</v>
       </c>
       <c r="F6">
-        <v>246.188</v>
+        <v>307.735</v>
       </c>
       <c r="G6">
         <v>173.9</v>
@@ -1901,45 +1901,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M6">
-        <v>12.3832564</v>
+        <v>15.940673</v>
       </c>
       <c r="N6">
-        <v>96.63307013061225</v>
+        <v>93.07565353061224</v>
       </c>
       <c r="O6">
-        <v>19.32661402612245</v>
+        <v>18.61513070612245</v>
       </c>
       <c r="P6">
-        <v>77.3064561044898</v>
+        <v>74.4605228244898</v>
       </c>
       <c r="Q6">
-        <v>144.1064561044898</v>
+        <v>141.2605228244898</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09774215457646576</v>
+        <v>0.09818308967473796</v>
       </c>
       <c r="T6">
-        <v>1.01244927257679</v>
+        <v>1.021043918354182</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.803526553048862</v>
+        <v>6.838878542368459</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09534593519100107</v>
+        <v>0.095321801988595</v>
       </c>
       <c r="C7">
-        <v>5894.270964007848</v>
+        <v>5835.661609560168</v>
       </c>
       <c r="D7">
-        <v>6028.105964007848</v>
+        <v>6031.043609560169</v>
       </c>
       <c r="E7">
-        <v>12.935</v>
+        <v>74.48200000000003</v>
       </c>
       <c r="F7">
-        <v>307.735</v>
+        <v>369.282</v>
       </c>
       <c r="G7">
         <v>173.9</v>
@@ -1983,45 +1983,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M7">
-        <v>15.940673</v>
+        <v>20.0520126</v>
       </c>
       <c r="N7">
-        <v>93.07565353061224</v>
+        <v>88.96431393061225</v>
       </c>
       <c r="O7">
-        <v>18.61513070612245</v>
+        <v>17.79286278612245</v>
       </c>
       <c r="P7">
-        <v>74.4605228244898</v>
+        <v>71.17145114448979</v>
       </c>
       <c r="Q7">
-        <v>141.2605228244898</v>
+        <v>137.9714511444898</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09818308967473796</v>
+        <v>0.09863340637084575</v>
       </c>
       <c r="T7">
-        <v>1.021043918354182</v>
+        <v>1.029821428935348</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04144</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.838878542368459</v>
+        <v>5.43667753982023</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.095321801988595</v>
+        <v>0.09519766878618895</v>
       </c>
       <c r="C8">
-        <v>5835.661609560168</v>
+        <v>5789.270238874289</v>
       </c>
       <c r="D8">
-        <v>6031.043609560169</v>
+        <v>6046.199238874289</v>
       </c>
       <c r="E8">
-        <v>74.48199999999997</v>
+        <v>136.0289999999999</v>
       </c>
       <c r="F8">
-        <v>369.282</v>
+        <v>430.829</v>
       </c>
       <c r="G8">
         <v>173.9</v>
@@ -2065,28 +2065,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M8">
-        <v>20.0520126</v>
+        <v>23.3940147</v>
       </c>
       <c r="N8">
-        <v>88.96431393061225</v>
+        <v>85.62231183061225</v>
       </c>
       <c r="O8">
-        <v>17.79286278612245</v>
+        <v>17.12446236612245</v>
       </c>
       <c r="P8">
-        <v>71.17145114448979</v>
+        <v>68.4978494644898</v>
       </c>
       <c r="Q8">
-        <v>137.9714511444898</v>
+        <v>135.2978494644898</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09863340637084575</v>
+        <v>0.09909340729697735</v>
       </c>
       <c r="T8">
-        <v>1.029821428935348</v>
+        <v>1.038787703184927</v>
       </c>
       <c r="U8">
         <v>0.0543</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.43667753982023</v>
+        <v>4.660009319845912</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09519766878618893</v>
+        <v>0.09513753558378289</v>
       </c>
       <c r="C9">
-        <v>5789.270238874292</v>
+        <v>5735.092421755367</v>
       </c>
       <c r="D9">
-        <v>6046.199238874292</v>
+        <v>6053.568421755368</v>
       </c>
       <c r="E9">
-        <v>136.029</v>
+        <v>197.576</v>
       </c>
       <c r="F9">
-        <v>430.829</v>
+        <v>492.376</v>
       </c>
       <c r="G9">
         <v>173.9</v>
@@ -2147,45 +2147,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M9">
-        <v>23.3940147</v>
+        <v>27.2283928</v>
       </c>
       <c r="N9">
-        <v>85.62231183061225</v>
+        <v>81.78793373061225</v>
       </c>
       <c r="O9">
-        <v>17.12446236612245</v>
+        <v>16.35758674612245</v>
       </c>
       <c r="P9">
-        <v>68.4978494644898</v>
+        <v>65.4303469844898</v>
       </c>
       <c r="Q9">
-        <v>135.2978494644898</v>
+        <v>132.2303469844898</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09909340729697735</v>
+        <v>0.09956340824324227</v>
       </c>
       <c r="T9">
-        <v>1.038787703184927</v>
+        <v>1.047948896439931</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.660009319845911</v>
+        <v>4.003773830184066</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09513753558378289</v>
+        <v>0.09502140238137682</v>
       </c>
       <c r="C10">
-        <v>5735.092421755367</v>
+        <v>5687.828238838789</v>
       </c>
       <c r="D10">
-        <v>6053.568421755368</v>
+        <v>6067.851238838789</v>
       </c>
       <c r="E10">
-        <v>197.576</v>
+        <v>259.123</v>
       </c>
       <c r="F10">
-        <v>492.376</v>
+        <v>553.923</v>
       </c>
       <c r="G10">
         <v>173.9</v>
@@ -2229,28 +2229,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M10">
-        <v>27.2283928</v>
+        <v>30.6319419</v>
       </c>
       <c r="N10">
-        <v>81.78793373061225</v>
+        <v>78.38438463061225</v>
       </c>
       <c r="O10">
-        <v>16.35758674612245</v>
+        <v>15.67687692612245</v>
       </c>
       <c r="P10">
-        <v>65.4303469844898</v>
+        <v>62.7075077044898</v>
       </c>
       <c r="Q10">
-        <v>132.2303469844898</v>
+        <v>129.5075077044898</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09956340824324227</v>
+        <v>0.1000437388806339</v>
       </c>
       <c r="T10">
-        <v>1.047948896439931</v>
+        <v>1.057311434601638</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>4.003773830184066</v>
+        <v>3.558910071274725</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09502140238137682</v>
+        <v>0.09490526917897074</v>
       </c>
       <c r="C11">
-        <v>5687.828238838789</v>
+        <v>5640.631613205372</v>
       </c>
       <c r="D11">
-        <v>6067.851238838789</v>
+        <v>6082.201613205372</v>
       </c>
       <c r="E11">
-        <v>259.123</v>
+        <v>320.6699999999999</v>
       </c>
       <c r="F11">
-        <v>553.923</v>
+        <v>615.4699999999999</v>
       </c>
       <c r="G11">
         <v>173.9</v>
@@ -2311,28 +2311,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M11">
-        <v>30.6319419</v>
+        <v>34.03549099999999</v>
       </c>
       <c r="N11">
-        <v>78.38438463061225</v>
+        <v>74.98083553061225</v>
       </c>
       <c r="O11">
-        <v>15.67687692612245</v>
+        <v>14.99616710612245</v>
       </c>
       <c r="P11">
-        <v>62.7075077044898</v>
+        <v>59.9846684244898</v>
       </c>
       <c r="Q11">
-        <v>129.5075077044898</v>
+        <v>126.7846684244898</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1000437388806339</v>
+        <v>0.1005347435321897</v>
       </c>
       <c r="T11">
-        <v>1.057311434601638</v>
+        <v>1.066882029166939</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.558910071274725</v>
+        <v>3.203019064147254</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09490526917897076</v>
+        <v>0.0950091359765647</v>
       </c>
       <c r="C12">
-        <v>5640.63161320537</v>
+        <v>5566.246777479395</v>
       </c>
       <c r="D12">
-        <v>6082.20161320537</v>
+        <v>6069.363777479395</v>
       </c>
       <c r="E12">
-        <v>320.67</v>
+        <v>382.2169999999999</v>
       </c>
       <c r="F12">
-        <v>615.47</v>
+        <v>677.0169999999999</v>
       </c>
       <c r="G12">
         <v>173.9</v>
@@ -2393,45 +2393,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M12">
-        <v>34.035491</v>
+        <v>39.1315826</v>
       </c>
       <c r="N12">
-        <v>74.98083553061224</v>
+        <v>69.88474393061225</v>
       </c>
       <c r="O12">
-        <v>14.99616710612245</v>
+        <v>13.97694878612245</v>
       </c>
       <c r="P12">
-        <v>59.98466842448979</v>
+        <v>55.9077951444898</v>
       </c>
       <c r="Q12">
-        <v>126.7846684244898</v>
+        <v>122.7077951444898</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1005347435321897</v>
+        <v>0.1010367819961401</v>
       </c>
       <c r="T12">
-        <v>1.06688202916694</v>
+        <v>1.076667693273034</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.203019064147253</v>
+        <v>2.785891070263339</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0950091359765647</v>
+        <v>0.09491300277415864</v>
       </c>
       <c r="C13">
-        <v>5566.246777479395</v>
+        <v>5516.579877321374</v>
       </c>
       <c r="D13">
-        <v>6069.363777479395</v>
+        <v>6081.243877321374</v>
       </c>
       <c r="E13">
-        <v>382.2169999999999</v>
+        <v>443.764</v>
       </c>
       <c r="F13">
-        <v>677.0169999999999</v>
+        <v>738.564</v>
       </c>
       <c r="G13">
         <v>173.9</v>
@@ -2475,28 +2475,28 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M13">
-        <v>39.1315826</v>
+        <v>42.6889992</v>
       </c>
       <c r="N13">
-        <v>69.88474393061225</v>
+        <v>66.32732733061225</v>
       </c>
       <c r="O13">
-        <v>13.97694878612245</v>
+        <v>13.26546546612245</v>
       </c>
       <c r="P13">
-        <v>55.9077951444898</v>
+        <v>53.0618618644898</v>
       </c>
       <c r="Q13">
-        <v>122.7077951444898</v>
+        <v>119.8618618644898</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1010367819961401</v>
+        <v>0.1015502304251803</v>
       </c>
       <c r="T13">
-        <v>1.076667693273034</v>
+        <v>1.086675758836085</v>
       </c>
       <c r="U13">
         <v>0.0578</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.785891070263339</v>
+        <v>2.553733481074727</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09491300277415864</v>
+        <v>0.09547206957175257</v>
       </c>
       <c r="C14">
-        <v>5516.579877321374</v>
+        <v>5386.587540350451</v>
       </c>
       <c r="D14">
-        <v>6081.243877321374</v>
+        <v>6012.798540350451</v>
       </c>
       <c r="E14">
-        <v>443.764</v>
+        <v>505.311</v>
       </c>
       <c r="F14">
-        <v>738.564</v>
+        <v>800.111</v>
       </c>
       <c r="G14">
         <v>173.9</v>
@@ -2557,45 +2557,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M14">
-        <v>42.6889992</v>
+        <v>51.2871151</v>
       </c>
       <c r="N14">
-        <v>66.32732733061225</v>
+        <v>57.72921143061225</v>
       </c>
       <c r="O14">
-        <v>13.26546546612245</v>
+        <v>11.54584228612245</v>
       </c>
       <c r="P14">
-        <v>53.0618618644898</v>
+        <v>46.1833691444898</v>
       </c>
       <c r="Q14">
-        <v>119.8618618644898</v>
+        <v>112.9833691444898</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1015502304251803</v>
+        <v>0.1020754822663823</v>
       </c>
       <c r="T14">
-        <v>1.086675758836085</v>
+        <v>1.09691389487185</v>
       </c>
       <c r="U14">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.553733481074727</v>
+        <v>2.125608475307129</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09547206957175257</v>
+        <v>0.09629993636934651</v>
       </c>
       <c r="C15">
-        <v>5386.587540350451</v>
+        <v>5226.470192939101</v>
       </c>
       <c r="D15">
-        <v>6012.798540350451</v>
+        <v>5914.228192939102</v>
       </c>
       <c r="E15">
-        <v>505.311</v>
+        <v>566.8579999999999</v>
       </c>
       <c r="F15">
-        <v>800.111</v>
+        <v>861.658</v>
       </c>
       <c r="G15">
         <v>173.9</v>
@@ -2639,45 +2639,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M15">
-        <v>51.2871151</v>
+        <v>61.95321020000001</v>
       </c>
       <c r="N15">
-        <v>57.72921143061225</v>
+        <v>47.06311633061224</v>
       </c>
       <c r="O15">
-        <v>11.54584228612245</v>
+        <v>9.412623266122448</v>
       </c>
       <c r="P15">
-        <v>46.1833691444898</v>
+        <v>37.65049306448979</v>
       </c>
       <c r="Q15">
-        <v>112.9833691444898</v>
+        <v>104.4504930644898</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1020754822663823</v>
+        <v>0.102612949266682</v>
       </c>
       <c r="T15">
-        <v>1.09691389487185</v>
+        <v>1.107390127094493</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.125608475307129</v>
+        <v>1.759655814100368</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09629993636934651</v>
+        <v>0.09678460316694044</v>
       </c>
       <c r="C16">
-        <v>5226.470192939101</v>
+        <v>5108.701709187902</v>
       </c>
       <c r="D16">
-        <v>5914.228192939102</v>
+        <v>5858.006709187902</v>
       </c>
       <c r="E16">
-        <v>566.8579999999999</v>
+        <v>628.4050000000002</v>
       </c>
       <c r="F16">
-        <v>861.658</v>
+        <v>923.2050000000002</v>
       </c>
       <c r="G16">
         <v>173.9</v>
@@ -2721,45 +2721,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M16">
-        <v>61.95321020000001</v>
+        <v>69.97893900000001</v>
       </c>
       <c r="N16">
-        <v>47.06311633061224</v>
+        <v>39.03738753061224</v>
       </c>
       <c r="O16">
-        <v>9.412623266122448</v>
+        <v>7.807477506122448</v>
       </c>
       <c r="P16">
-        <v>37.65049306448979</v>
+        <v>31.22991002448979</v>
       </c>
       <c r="Q16">
-        <v>104.4504930644898</v>
+        <v>98.02991002448979</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.102612949266682</v>
+        <v>0.1031630625493417</v>
       </c>
       <c r="T16">
-        <v>1.107390127094493</v>
+        <v>1.118112858898845</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>1.759655814100368</v>
+        <v>1.557844804286219</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09678460316694043</v>
+        <v>0.1026706169289684</v>
       </c>
       <c r="C17">
-        <v>5108.701709187903</v>
+        <v>4440.860809626412</v>
       </c>
       <c r="D17">
-        <v>5858.006709187904</v>
+        <v>5251.712809626413</v>
       </c>
       <c r="E17">
-        <v>628.405</v>
+        <v>689.952</v>
       </c>
       <c r="F17">
-        <v>923.2049999999999</v>
+        <v>984.752</v>
       </c>
       <c r="G17">
         <v>173.9</v>
@@ -2803,45 +2803,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M17">
-        <v>69.978939</v>
+        <v>116.7915872</v>
       </c>
       <c r="N17">
-        <v>39.03738753061225</v>
+        <v>-7.775260669387762</v>
       </c>
       <c r="O17">
-        <v>7.80747750612245</v>
+        <v>-1.555052133877552</v>
       </c>
       <c r="P17">
-        <v>31.2299100244898</v>
+        <v>-6.22020853551021</v>
       </c>
       <c r="Q17">
-        <v>98.02991002448981</v>
+        <v>60.5797914644898</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1031630625493417</v>
+        <v>0.1038537571594229</v>
       </c>
       <c r="T17">
-        <v>1.118112858898845</v>
+        <v>1.13157578243853</v>
       </c>
       <c r="U17">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V17">
-        <v>0.2</v>
+        <v>0.1866852384563059</v>
       </c>
       <c r="W17">
-        <v>0.06064000000000001</v>
+        <v>0.09645913071908213</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y17">
-        <v>1.557844804286219</v>
+        <v>0.9334261922815297</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1026706169289684</v>
+        <v>0.1033986169289684</v>
       </c>
       <c r="C18">
-        <v>4440.860809626412</v>
+        <v>4312.936401118097</v>
       </c>
       <c r="D18">
-        <v>5251.712809626413</v>
+        <v>5185.335401118097</v>
       </c>
       <c r="E18">
-        <v>689.952</v>
+        <v>751.499</v>
       </c>
       <c r="F18">
-        <v>984.752</v>
+        <v>1046.299</v>
       </c>
       <c r="G18">
         <v>173.9</v>
@@ -2885,37 +2885,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M18">
-        <v>116.7915872</v>
+        <v>124.0910614</v>
       </c>
       <c r="N18">
-        <v>-7.775260669387762</v>
+        <v>-15.07473486938777</v>
       </c>
       <c r="O18">
-        <v>-1.555052133877552</v>
+        <v>-3.014946973877554</v>
       </c>
       <c r="P18">
-        <v>-6.22020853551021</v>
+        <v>-12.05978789551022</v>
       </c>
       <c r="Q18">
-        <v>60.5797914644898</v>
+        <v>54.7402121044898</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1038537571594229</v>
+        <v>0.1045532000167653</v>
       </c>
       <c r="T18">
-        <v>1.13157578243853</v>
+        <v>1.14520922560044</v>
       </c>
       <c r="U18">
         <v>0.1186</v>
       </c>
       <c r="V18">
-        <v>0.1866852384563059</v>
+        <v>0.1757037538412291</v>
       </c>
       <c r="W18">
-        <v>0.09645913071908213</v>
+        <v>0.09776153479443023</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.9334261922815297</v>
+        <v>0.8785187692061456</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1033986169289684</v>
+        <v>0.1041266169289684</v>
       </c>
       <c r="C19">
-        <v>4312.936401118097</v>
+        <v>4186.668963507063</v>
       </c>
       <c r="D19">
-        <v>5185.335401118097</v>
+        <v>5120.614963507064</v>
       </c>
       <c r="E19">
-        <v>751.499</v>
+        <v>813.046</v>
       </c>
       <c r="F19">
-        <v>1046.299</v>
+        <v>1107.846</v>
       </c>
       <c r="G19">
         <v>173.9</v>
@@ -2967,37 +2967,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M19">
-        <v>124.0910614</v>
+        <v>131.3905356</v>
       </c>
       <c r="N19">
-        <v>-15.07473486938777</v>
+        <v>-22.37420906938777</v>
       </c>
       <c r="O19">
-        <v>-3.014946973877554</v>
+        <v>-4.474841813877555</v>
       </c>
       <c r="P19">
-        <v>-12.05978789551022</v>
+        <v>-17.89936725551022</v>
       </c>
       <c r="Q19">
-        <v>54.7402121044898</v>
+        <v>48.90063274448979</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1045532000167653</v>
+        <v>0.1052697024559942</v>
       </c>
       <c r="T19">
-        <v>1.14520922560044</v>
+        <v>1.159175191766298</v>
       </c>
       <c r="U19">
         <v>0.1186</v>
       </c>
       <c r="V19">
-        <v>0.1757037538412291</v>
+        <v>0.1659424341833831</v>
       </c>
       <c r="W19">
-        <v>0.09776153479443023</v>
+        <v>0.09891922730585077</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.8785187692061456</v>
+        <v>0.8297121709169152</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1041266169289684</v>
+        <v>0.1210872523599711</v>
       </c>
       <c r="C20">
-        <v>4186.668963507063</v>
+        <v>2971.55504671576</v>
       </c>
       <c r="D20">
-        <v>5120.614963507063</v>
+        <v>3967.04804671576</v>
       </c>
       <c r="E20">
-        <v>813.046</v>
+        <v>874.5930000000001</v>
       </c>
       <c r="F20">
-        <v>1107.846</v>
+        <v>1169.393</v>
       </c>
       <c r="G20">
         <v>173.9</v>
@@ -3049,45 +3049,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M20">
-        <v>131.3905356</v>
+        <v>234.8141144</v>
       </c>
       <c r="N20">
-        <v>-22.37420906938777</v>
+        <v>-125.7977878693878</v>
       </c>
       <c r="O20">
-        <v>-4.474841813877555</v>
+        <v>-25.15955757387756</v>
       </c>
       <c r="P20">
-        <v>-17.89936725551022</v>
+        <v>-100.6382302955102</v>
       </c>
       <c r="Q20">
-        <v>48.90063274448979</v>
+        <v>-33.83823029551021</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1052697024559942</v>
+        <v>0.106762705487553</v>
       </c>
       <c r="T20">
-        <v>1.159175191766298</v>
+        <v>1.188276599776462</v>
       </c>
       <c r="U20">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.1659424341833831</v>
+        <v>0.09285329956350549</v>
       </c>
       <c r="W20">
-        <v>0.09891922730585077</v>
+        <v>0.1821550574476481</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.8297121709169152</v>
+        <v>0.4642664978175274</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1210872523599711</v>
+        <v>0.1226372523599711</v>
       </c>
       <c r="C21">
-        <v>2971.55504671576</v>
+        <v>2829.982742796736</v>
       </c>
       <c r="D21">
-        <v>3967.04804671576</v>
+        <v>3887.022742796736</v>
       </c>
       <c r="E21">
-        <v>874.5930000000001</v>
+        <v>936.1400000000001</v>
       </c>
       <c r="F21">
-        <v>1169.393</v>
+        <v>1230.94</v>
       </c>
       <c r="G21">
         <v>173.9</v>
@@ -3131,37 +3131,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M21">
-        <v>234.8141144</v>
+        <v>247.172752</v>
       </c>
       <c r="N21">
-        <v>-125.7977878693878</v>
+        <v>-138.1564254693878</v>
       </c>
       <c r="O21">
-        <v>-25.15955757387756</v>
+        <v>-27.63128509387756</v>
       </c>
       <c r="P21">
-        <v>-100.6382302955102</v>
+        <v>-110.5251403755102</v>
       </c>
       <c r="Q21">
-        <v>-33.83823029551021</v>
+        <v>-43.72514037551022</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.106762705487553</v>
+        <v>0.1075247393061474</v>
       </c>
       <c r="T21">
-        <v>1.188276599776462</v>
+        <v>1.203130057273668</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.09285329956350549</v>
+        <v>0.08821063458533021</v>
       </c>
       <c r="W21">
-        <v>0.1821550574476481</v>
+        <v>0.1830873045752657</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4642664978175274</v>
+        <v>0.441053172926651</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1226372523599711</v>
+        <v>0.1241872523599711</v>
       </c>
       <c r="C22">
-        <v>2829.982742796736</v>
+        <v>2691.575219306674</v>
       </c>
       <c r="D22">
-        <v>3887.022742796736</v>
+        <v>3810.162219306674</v>
       </c>
       <c r="E22">
-        <v>936.1400000000001</v>
+        <v>997.6870000000001</v>
       </c>
       <c r="F22">
-        <v>1230.94</v>
+        <v>1292.487</v>
       </c>
       <c r="G22">
         <v>173.9</v>
@@ -3213,37 +3213,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M22">
-        <v>247.172752</v>
+        <v>259.5313896</v>
       </c>
       <c r="N22">
-        <v>-138.1564254693878</v>
+        <v>-150.5150630693878</v>
       </c>
       <c r="O22">
-        <v>-27.63128509387756</v>
+        <v>-30.10301261387755</v>
       </c>
       <c r="P22">
-        <v>-110.5251403755102</v>
+        <v>-120.4120504555102</v>
       </c>
       <c r="Q22">
-        <v>-43.72514037551022</v>
+        <v>-53.6120504555102</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1075247393061474</v>
+        <v>0.1083060651201493</v>
       </c>
       <c r="T22">
-        <v>1.203130057273668</v>
+        <v>1.218359551669537</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.08821063458533021</v>
+        <v>0.08401012817650498</v>
       </c>
       <c r="W22">
-        <v>0.1830873045752657</v>
+        <v>0.1839307662621578</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.441053172926651</v>
+        <v>0.4200506408825249</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1241872523599711</v>
+        <v>0.1257372523599711</v>
       </c>
       <c r="C23">
-        <v>2691.575219306675</v>
+        <v>2556.148378987286</v>
       </c>
       <c r="D23">
-        <v>3810.162219306674</v>
+        <v>3736.282378987286</v>
       </c>
       <c r="E23">
-        <v>997.6869999999999</v>
+        <v>1059.234</v>
       </c>
       <c r="F23">
-        <v>1292.487</v>
+        <v>1354.034</v>
       </c>
       <c r="G23">
         <v>173.9</v>
@@ -3295,37 +3295,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M23">
-        <v>259.5313896</v>
+        <v>271.8900272</v>
       </c>
       <c r="N23">
-        <v>-150.5150630693877</v>
+        <v>-162.8737006693877</v>
       </c>
       <c r="O23">
-        <v>-30.10301261387754</v>
+        <v>-32.57474013387755</v>
       </c>
       <c r="P23">
-        <v>-120.4120504555102</v>
+        <v>-130.2989605355102</v>
       </c>
       <c r="Q23">
-        <v>-53.61205045551016</v>
+        <v>-63.49896053551015</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1083060651201493</v>
+        <v>0.109107424929382</v>
       </c>
       <c r="T23">
-        <v>1.218359551669537</v>
+        <v>1.23397954592171</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.08401012817650499</v>
+        <v>0.08019148598666385</v>
       </c>
       <c r="W23">
-        <v>0.1839307662621578</v>
+        <v>0.1846975496138779</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.420050640882525</v>
+        <v>0.4009574299333193</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1257372523599711</v>
+        <v>0.1272872523599711</v>
       </c>
       <c r="C24">
-        <v>2556.148378987286</v>
+        <v>2423.532131715979</v>
       </c>
       <c r="D24">
-        <v>3736.282378987286</v>
+        <v>3665.213131715979</v>
       </c>
       <c r="E24">
-        <v>1059.234</v>
+        <v>1120.781</v>
       </c>
       <c r="F24">
-        <v>1354.034</v>
+        <v>1415.581</v>
       </c>
       <c r="G24">
         <v>173.9</v>
@@ -3377,37 +3377,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M24">
-        <v>271.8900272</v>
+        <v>284.2486648</v>
       </c>
       <c r="N24">
-        <v>-162.8737006693877</v>
+        <v>-175.2323382693878</v>
       </c>
       <c r="O24">
-        <v>-32.57474013387755</v>
+        <v>-35.04646765387756</v>
       </c>
       <c r="P24">
-        <v>-130.2989605355102</v>
+        <v>-140.1858706155102</v>
       </c>
       <c r="Q24">
-        <v>-63.49896053551015</v>
+        <v>-73.38587061551021</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.109107424929382</v>
+        <v>0.1099295992791142</v>
       </c>
       <c r="T24">
-        <v>1.23397954592171</v>
+        <v>1.250005254310304</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.08019148598666385</v>
+        <v>0.07670489963941758</v>
       </c>
       <c r="W24">
-        <v>0.1846975496138779</v>
+        <v>0.1853976561524049</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.4009574299333193</v>
+        <v>0.3835244981970879</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1272872523599711</v>
+        <v>0.1288372523599711</v>
       </c>
       <c r="C25">
-        <v>2423.532131715979</v>
+        <v>2293.569087197405</v>
       </c>
       <c r="D25">
-        <v>3665.213131715979</v>
+        <v>3596.797087197405</v>
       </c>
       <c r="E25">
-        <v>1120.781</v>
+        <v>1182.328</v>
       </c>
       <c r="F25">
-        <v>1415.581</v>
+        <v>1477.128</v>
       </c>
       <c r="G25">
         <v>173.9</v>
@@ -3459,37 +3459,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M25">
-        <v>284.2486648</v>
+        <v>296.6073024</v>
       </c>
       <c r="N25">
-        <v>-175.2323382693878</v>
+        <v>-187.5909758693878</v>
       </c>
       <c r="O25">
-        <v>-35.04646765387756</v>
+        <v>-37.51819517387756</v>
       </c>
       <c r="P25">
-        <v>-140.1858706155102</v>
+        <v>-150.0727806955102</v>
       </c>
       <c r="Q25">
-        <v>-73.38587061551021</v>
+        <v>-83.27278069551022</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1099295992791142</v>
+        <v>0.1107734097959447</v>
       </c>
       <c r="T25">
-        <v>1.250005254310304</v>
+        <v>1.266452691867019</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.07670489963941758</v>
+        <v>0.07350886215444184</v>
       </c>
       <c r="W25">
-        <v>0.1853976561524049</v>
+        <v>0.1860394204793881</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3835244981970879</v>
+        <v>0.3675443107722092</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1288372523599711</v>
+        <v>0.1303872523599711</v>
       </c>
       <c r="C26">
-        <v>2293.569087197405</v>
+        <v>2166.113391387889</v>
       </c>
       <c r="D26">
-        <v>3596.797087197405</v>
+        <v>3530.888391387889</v>
       </c>
       <c r="E26">
-        <v>1182.328</v>
+        <v>1243.875</v>
       </c>
       <c r="F26">
-        <v>1477.128</v>
+        <v>1538.675</v>
       </c>
       <c r="G26">
         <v>173.9</v>
@@ -3541,37 +3541,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M26">
-        <v>296.6073024</v>
+        <v>308.96594</v>
       </c>
       <c r="N26">
-        <v>-187.5909758693877</v>
+        <v>-199.9496134693877</v>
       </c>
       <c r="O26">
-        <v>-37.51819517387755</v>
+        <v>-39.98992269387755</v>
       </c>
       <c r="P26">
-        <v>-150.0727806955102</v>
+        <v>-159.9596907755102</v>
       </c>
       <c r="Q26">
-        <v>-83.27278069551016</v>
+        <v>-93.15969077551017</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1107734097959447</v>
+        <v>0.1116397219265573</v>
       </c>
       <c r="T26">
-        <v>1.266452691867018</v>
+        <v>1.283338727758579</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.07350886215444186</v>
+        <v>0.07056850766826418</v>
       </c>
       <c r="W26">
-        <v>0.1860394204793881</v>
+        <v>0.1866298436602126</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3675443107722093</v>
+        <v>0.3528425383413208</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1303872523599711</v>
+        <v>0.1319372523599711</v>
       </c>
       <c r="C27">
-        <v>2166.113391387889</v>
+        <v>2041.029688547872</v>
       </c>
       <c r="D27">
-        <v>3530.888391387889</v>
+        <v>3467.351688547872</v>
       </c>
       <c r="E27">
-        <v>1243.875</v>
+        <v>1305.422</v>
       </c>
       <c r="F27">
-        <v>1538.675</v>
+        <v>1600.222</v>
       </c>
       <c r="G27">
         <v>173.9</v>
@@ -3623,37 +3623,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M27">
-        <v>308.96594</v>
+        <v>321.3245776</v>
       </c>
       <c r="N27">
-        <v>-199.9496134693877</v>
+        <v>-212.3082510693878</v>
       </c>
       <c r="O27">
-        <v>-39.98992269387755</v>
+        <v>-42.46165021387755</v>
       </c>
       <c r="P27">
-        <v>-159.9596907755102</v>
+        <v>-169.8466008555102</v>
       </c>
       <c r="Q27">
-        <v>-93.15969077551017</v>
+        <v>-103.0466008555102</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1116397219265573</v>
+        <v>0.1125294478985378</v>
       </c>
       <c r="T27">
-        <v>1.283338727758579</v>
+        <v>1.30068114299856</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.07056850766826418</v>
+        <v>0.06785433429640786</v>
       </c>
       <c r="W27">
-        <v>0.1866298436602126</v>
+        <v>0.1871748496732813</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3528425383413208</v>
+        <v>0.3392716714820393</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1319372523599711</v>
+        <v>0.1334872523599711</v>
       </c>
       <c r="C28">
-        <v>2041.029688547872</v>
+        <v>1918.19219337776</v>
       </c>
       <c r="D28">
-        <v>3467.351688547872</v>
+        <v>3406.06119337776</v>
       </c>
       <c r="E28">
-        <v>1305.422</v>
+        <v>1366.969</v>
       </c>
       <c r="F28">
-        <v>1600.222</v>
+        <v>1661.769</v>
       </c>
       <c r="G28">
         <v>173.9</v>
@@ -3705,37 +3705,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M28">
-        <v>321.3245776</v>
+        <v>333.6832152</v>
       </c>
       <c r="N28">
-        <v>-212.3082510693878</v>
+        <v>-224.6668886693878</v>
       </c>
       <c r="O28">
-        <v>-42.46165021387755</v>
+        <v>-44.93337773387756</v>
       </c>
       <c r="P28">
-        <v>-169.8466008555102</v>
+        <v>-179.7335109355102</v>
       </c>
       <c r="Q28">
-        <v>-103.0466008555102</v>
+        <v>-112.9335109355102</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1125294478985378</v>
+        <v>0.1134435499245451</v>
       </c>
       <c r="T28">
-        <v>1.30068114299856</v>
+        <v>1.318498692902649</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.06785433429640786</v>
+        <v>0.06534121080394832</v>
       </c>
       <c r="W28">
-        <v>0.1871748496732813</v>
+        <v>0.1876794848705672</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3392716714820393</v>
+        <v>0.3267060540197415</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1334872523599711</v>
+        <v>0.1350372523599711</v>
       </c>
       <c r="C29">
-        <v>1918.19219337776</v>
+        <v>1797.483859852616</v>
       </c>
       <c r="D29">
-        <v>3406.06119337776</v>
+        <v>3346.899859852616</v>
       </c>
       <c r="E29">
-        <v>1366.969</v>
+        <v>1428.516</v>
       </c>
       <c r="F29">
-        <v>1661.769</v>
+        <v>1723.316</v>
       </c>
       <c r="G29">
         <v>173.9</v>
@@ -3787,37 +3787,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M29">
-        <v>333.6832152</v>
+        <v>346.0418528</v>
       </c>
       <c r="N29">
-        <v>-224.6668886693878</v>
+        <v>-237.0255262693878</v>
       </c>
       <c r="O29">
-        <v>-44.93337773387756</v>
+        <v>-47.40510525387756</v>
       </c>
       <c r="P29">
-        <v>-179.7335109355102</v>
+        <v>-189.6204210155102</v>
       </c>
       <c r="Q29">
-        <v>-112.9335109355102</v>
+        <v>-122.8204210155102</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1134435499245451</v>
+        <v>0.1143830436734972</v>
       </c>
       <c r="T29">
-        <v>1.318498692902649</v>
+        <v>1.33681117474852</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.06534121080394832</v>
+        <v>0.06300759613237873</v>
       </c>
       <c r="W29">
-        <v>0.1876794848705672</v>
+        <v>0.1881480746966184</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3267060540197415</v>
+        <v>0.3150379806618936</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1350372523599711</v>
+        <v>0.1365872523599711</v>
       </c>
       <c r="C30">
-        <v>1797.483859852616</v>
+        <v>1678.795635199155</v>
       </c>
       <c r="D30">
-        <v>3346.899859852616</v>
+        <v>3289.758635199155</v>
       </c>
       <c r="E30">
-        <v>1428.516</v>
+        <v>1490.063</v>
       </c>
       <c r="F30">
-        <v>1723.316</v>
+        <v>1784.863</v>
       </c>
       <c r="G30">
         <v>173.9</v>
@@ -3869,37 +3869,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M30">
-        <v>346.0418528</v>
+        <v>358.4004904</v>
       </c>
       <c r="N30">
-        <v>-237.0255262693878</v>
+        <v>-249.3841638693878</v>
       </c>
       <c r="O30">
-        <v>-47.40510525387756</v>
+        <v>-49.87683277387756</v>
       </c>
       <c r="P30">
-        <v>-189.6204210155102</v>
+        <v>-199.5073310955102</v>
       </c>
       <c r="Q30">
-        <v>-122.8204210155102</v>
+        <v>-132.7073310955102</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1143830436734972</v>
+        <v>0.1153490020350957</v>
       </c>
       <c r="T30">
-        <v>1.33681117474852</v>
+        <v>1.355639501153429</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.06300759613237873</v>
+        <v>0.06083492040367601</v>
       </c>
       <c r="W30">
-        <v>0.1881480746966184</v>
+        <v>0.1885843479829419</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3150379806618936</v>
+        <v>0.3041746020183801</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1365872523599711</v>
+        <v>0.1381372523599711</v>
       </c>
       <c r="C31">
-        <v>1678.795635199156</v>
+        <v>1562.02578901049</v>
       </c>
       <c r="D31">
-        <v>3289.758635199156</v>
+        <v>3234.53578901049</v>
       </c>
       <c r="E31">
-        <v>1490.063</v>
+        <v>1551.61</v>
       </c>
       <c r="F31">
-        <v>1784.863</v>
+        <v>1846.41</v>
       </c>
       <c r="G31">
         <v>173.9</v>
@@ -3951,37 +3951,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M31">
-        <v>358.4004904</v>
+        <v>370.759128</v>
       </c>
       <c r="N31">
-        <v>-249.3841638693877</v>
+        <v>-261.7428014693877</v>
       </c>
       <c r="O31">
-        <v>-49.87683277387755</v>
+        <v>-52.34856029387754</v>
       </c>
       <c r="P31">
-        <v>-199.5073310955102</v>
+        <v>-209.3942411755102</v>
       </c>
       <c r="Q31">
-        <v>-132.7073310955102</v>
+        <v>-142.5942411755101</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1153490020350957</v>
+        <v>0.1163425592070257</v>
       </c>
       <c r="T31">
-        <v>1.355639501153429</v>
+        <v>1.375005779741334</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.06083492040367602</v>
+        <v>0.05880708972355349</v>
       </c>
       <c r="W31">
-        <v>0.1885843479829419</v>
+        <v>0.1889915363835105</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3041746020183801</v>
+        <v>0.2940354486177675</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1381372523599711</v>
+        <v>0.1396872523599711</v>
       </c>
       <c r="C32">
-        <v>1562.02578901049</v>
+        <v>1447.079308815416</v>
       </c>
       <c r="D32">
-        <v>3234.53578901049</v>
+        <v>3181.136308815416</v>
       </c>
       <c r="E32">
-        <v>1551.61</v>
+        <v>1613.157</v>
       </c>
       <c r="F32">
-        <v>1846.41</v>
+        <v>1907.957</v>
       </c>
       <c r="G32">
         <v>173.9</v>
@@ -4033,37 +4033,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M32">
-        <v>370.759128</v>
+        <v>383.1177656</v>
       </c>
       <c r="N32">
-        <v>-261.7428014693877</v>
+        <v>-274.1014390693878</v>
       </c>
       <c r="O32">
-        <v>-52.34856029387754</v>
+        <v>-54.82028781387756</v>
       </c>
       <c r="P32">
-        <v>-209.3942411755102</v>
+        <v>-219.2811512555102</v>
       </c>
       <c r="Q32">
-        <v>-142.5942411755101</v>
+        <v>-152.4811512555102</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1163425592070257</v>
+        <v>0.1173649151375623</v>
       </c>
       <c r="T32">
-        <v>1.375005779741334</v>
+        <v>1.394933399737586</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.05880708972355349</v>
+        <v>0.05691008682924531</v>
       </c>
       <c r="W32">
-        <v>0.1889915363835105</v>
+        <v>0.1893724545646875</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2940354486177675</v>
+        <v>0.2845504341462265</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1396872523599711</v>
+        <v>0.1412372523599711</v>
       </c>
       <c r="C33">
-        <v>1447.079308815416</v>
+        <v>1333.867354547182</v>
       </c>
       <c r="D33">
-        <v>3181.136308815416</v>
+        <v>3129.471354547181</v>
       </c>
       <c r="E33">
-        <v>1613.157</v>
+        <v>1674.704</v>
       </c>
       <c r="F33">
-        <v>1907.957</v>
+        <v>1969.504</v>
       </c>
       <c r="G33">
         <v>173.9</v>
@@ -4115,37 +4115,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M33">
-        <v>383.1177656</v>
+        <v>395.4764032</v>
       </c>
       <c r="N33">
-        <v>-274.1014390693878</v>
+        <v>-286.4600766693877</v>
       </c>
       <c r="O33">
-        <v>-54.82028781387756</v>
+        <v>-57.29201533387754</v>
       </c>
       <c r="P33">
-        <v>-219.2811512555102</v>
+        <v>-229.1680613355102</v>
       </c>
       <c r="Q33">
-        <v>-152.4811512555102</v>
+        <v>-162.3680613355102</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1173649151375623</v>
+        <v>0.1184173403601735</v>
       </c>
       <c r="T33">
-        <v>1.394933399737586</v>
+        <v>1.415447126204315</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.05691008682924531</v>
+        <v>0.05513164661583139</v>
       </c>
       <c r="W33">
-        <v>0.1893724545646875</v>
+        <v>0.1897295653595411</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2845504341462265</v>
+        <v>0.275658233079157</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1412372523599711</v>
+        <v>0.1427872523599711</v>
       </c>
       <c r="C34">
-        <v>1333.867354547182</v>
+        <v>1222.306765322644</v>
       </c>
       <c r="D34">
-        <v>3129.471354547181</v>
+        <v>3079.457765322643</v>
       </c>
       <c r="E34">
-        <v>1674.704</v>
+        <v>1736.251</v>
       </c>
       <c r="F34">
-        <v>1969.504</v>
+        <v>2031.051</v>
       </c>
       <c r="G34">
         <v>173.9</v>
@@ -4197,37 +4197,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M34">
-        <v>395.4764032</v>
+        <v>407.8350408</v>
       </c>
       <c r="N34">
-        <v>-286.4600766693877</v>
+        <v>-298.8187142693878</v>
       </c>
       <c r="O34">
-        <v>-57.29201533387754</v>
+        <v>-59.76374285387756</v>
       </c>
       <c r="P34">
-        <v>-229.1680613355102</v>
+        <v>-239.0549714155102</v>
       </c>
       <c r="Q34">
-        <v>-162.3680613355102</v>
+        <v>-172.2549714155102</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1184173403601735</v>
+        <v>0.1195011812610716</v>
       </c>
       <c r="T34">
-        <v>1.415447126204315</v>
+        <v>1.436573202714827</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.05513164661583139</v>
+        <v>0.05346099065777589</v>
       </c>
       <c r="W34">
-        <v>0.1897295653595411</v>
+        <v>0.1900650330759186</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.275658233079157</v>
+        <v>0.2673049532888794</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1427872523599711</v>
+        <v>0.1443372523599711</v>
       </c>
       <c r="C35">
-        <v>1222.306765322644</v>
+        <v>1112.31961277188</v>
       </c>
       <c r="D35">
-        <v>3079.457765322643</v>
+        <v>3031.01761277188</v>
       </c>
       <c r="E35">
-        <v>1736.251</v>
+        <v>1797.798</v>
       </c>
       <c r="F35">
-        <v>2031.051</v>
+        <v>2092.598</v>
       </c>
       <c r="G35">
         <v>173.9</v>
@@ -4279,37 +4279,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M35">
-        <v>407.8350408</v>
+        <v>420.1936784</v>
       </c>
       <c r="N35">
-        <v>-298.8187142693878</v>
+        <v>-311.1773518693877</v>
       </c>
       <c r="O35">
-        <v>-59.76374285387756</v>
+        <v>-62.23547037387755</v>
       </c>
       <c r="P35">
-        <v>-239.0549714155102</v>
+        <v>-248.9418814955102</v>
       </c>
       <c r="Q35">
-        <v>-172.2549714155102</v>
+        <v>-182.1418814955102</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1195011812610716</v>
+        <v>0.1206178658256333</v>
       </c>
       <c r="T35">
-        <v>1.436573202714827</v>
+        <v>1.458339463362021</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.05346099065777589</v>
+        <v>0.05188860857960601</v>
       </c>
       <c r="W35">
-        <v>0.1900650330759186</v>
+        <v>0.1903807673972151</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2673049532888794</v>
+        <v>0.2594430428980301</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1443372523599711</v>
+        <v>0.1458872523599711</v>
       </c>
       <c r="C36">
-        <v>1112.31961277188</v>
+        <v>1003.832795871927</v>
       </c>
       <c r="D36">
-        <v>3031.01761277188</v>
+        <v>2984.077795871927</v>
       </c>
       <c r="E36">
-        <v>1797.798</v>
+        <v>1859.345</v>
       </c>
       <c r="F36">
-        <v>2092.598</v>
+        <v>2154.145</v>
       </c>
       <c r="G36">
         <v>173.9</v>
@@ -4361,37 +4361,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M36">
-        <v>420.1936784</v>
+        <v>432.552316</v>
       </c>
       <c r="N36">
-        <v>-311.1773518693877</v>
+        <v>-323.5359894693878</v>
       </c>
       <c r="O36">
-        <v>-62.23547037387755</v>
+        <v>-64.70719789387756</v>
       </c>
       <c r="P36">
-        <v>-248.9418814955102</v>
+        <v>-258.8287915755103</v>
       </c>
       <c r="Q36">
-        <v>-182.1418814955102</v>
+        <v>-192.0287915755102</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1206178658256333</v>
+        <v>0.1217689099152584</v>
       </c>
       <c r="T36">
-        <v>1.458339463362021</v>
+        <v>1.480775455106053</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.05188860857960601</v>
+        <v>0.05040607690590299</v>
       </c>
       <c r="W36">
-        <v>0.1903807673972151</v>
+        <v>0.1906784597572947</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2594430428980301</v>
+        <v>0.2520303845295149</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1458872523599711</v>
+        <v>0.1474372523599711</v>
       </c>
       <c r="C37">
-        <v>1003.832795871927</v>
+        <v>896.777672854002</v>
       </c>
       <c r="D37">
-        <v>2984.077795871927</v>
+        <v>2938.569672854002</v>
       </c>
       <c r="E37">
-        <v>1859.345</v>
+        <v>1920.892</v>
       </c>
       <c r="F37">
-        <v>2154.145</v>
+        <v>2215.692</v>
       </c>
       <c r="G37">
         <v>173.9</v>
@@ -4443,37 +4443,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M37">
-        <v>432.552316</v>
+        <v>444.9109536</v>
       </c>
       <c r="N37">
-        <v>-323.5359894693878</v>
+        <v>-335.8946270693878</v>
       </c>
       <c r="O37">
-        <v>-64.70719789387756</v>
+        <v>-67.17892541387755</v>
       </c>
       <c r="P37">
-        <v>-258.8287915755103</v>
+        <v>-268.7157016555102</v>
       </c>
       <c r="Q37">
-        <v>-192.0287915755102</v>
+        <v>-201.9157016555102</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1217689099152584</v>
+        <v>0.1229559241326843</v>
       </c>
       <c r="T37">
-        <v>1.480775455106053</v>
+        <v>1.503912571592085</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.05040607690590299</v>
+        <v>0.04900590810296124</v>
       </c>
       <c r="W37">
-        <v>0.1906784597572947</v>
+        <v>0.1909596136529254</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2520303845295149</v>
+        <v>0.2450295405148062</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1474372523599711</v>
+        <v>0.1489872523599711</v>
       </c>
       <c r="C38">
-        <v>896.7776728540016</v>
+        <v>791.0897262859685</v>
       </c>
       <c r="D38">
-        <v>2938.569672854002</v>
+        <v>2894.428726285968</v>
       </c>
       <c r="E38">
-        <v>1920.892</v>
+        <v>1982.439</v>
       </c>
       <c r="F38">
-        <v>2215.692</v>
+        <v>2277.239</v>
       </c>
       <c r="G38">
         <v>173.9</v>
@@ -4525,37 +4525,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M38">
-        <v>444.9109536</v>
+        <v>457.2695912</v>
       </c>
       <c r="N38">
-        <v>-335.8946270693878</v>
+        <v>-348.2532646693878</v>
       </c>
       <c r="O38">
-        <v>-67.17892541387755</v>
+        <v>-69.65065293387757</v>
       </c>
       <c r="P38">
-        <v>-268.7157016555102</v>
+        <v>-278.6026117355103</v>
       </c>
       <c r="Q38">
-        <v>-201.9157016555102</v>
+        <v>-211.8026117355103</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1229559241326843</v>
+        <v>0.1241806213411396</v>
       </c>
       <c r="T38">
-        <v>1.503912571592085</v>
+        <v>1.527784199712594</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.04900590810296124</v>
+        <v>0.0476814241001785</v>
       </c>
       <c r="W38">
-        <v>0.1909596136529254</v>
+        <v>0.1912255700406842</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2450295405148062</v>
+        <v>0.2384071205008924</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1489872523599711</v>
+        <v>0.1505372523599711</v>
       </c>
       <c r="C39">
-        <v>791.0897262859685</v>
+        <v>686.708257893345</v>
       </c>
       <c r="D39">
-        <v>2894.428726285968</v>
+        <v>2851.594257893345</v>
       </c>
       <c r="E39">
-        <v>1982.439</v>
+        <v>2043.986</v>
       </c>
       <c r="F39">
-        <v>2277.239</v>
+        <v>2338.786</v>
       </c>
       <c r="G39">
         <v>173.9</v>
@@ -4607,37 +4607,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M39">
-        <v>457.2695912</v>
+        <v>469.6282288</v>
       </c>
       <c r="N39">
-        <v>-348.2532646693878</v>
+        <v>-360.6119022693878</v>
       </c>
       <c r="O39">
-        <v>-69.65065293387757</v>
+        <v>-72.12238045387755</v>
       </c>
       <c r="P39">
-        <v>-278.6026117355103</v>
+        <v>-288.4895218155102</v>
       </c>
       <c r="Q39">
-        <v>-211.8026117355103</v>
+        <v>-221.6895218155102</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1241806213411396</v>
+        <v>0.125444824911158</v>
       </c>
       <c r="T39">
-        <v>1.527784199712594</v>
+        <v>1.55242588035312</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.0476814241001785</v>
+        <v>0.04642664978175275</v>
       </c>
       <c r="W39">
-        <v>0.1912255700406842</v>
+        <v>0.1914775287238241</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2384071205008924</v>
+        <v>0.2321332489087637</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1505372523599711</v>
+        <v>0.1520872523599711</v>
       </c>
       <c r="C40">
-        <v>686.708257893345</v>
+        <v>583.5761100830955</v>
       </c>
       <c r="D40">
-        <v>2851.594257893345</v>
+        <v>2810.009110083095</v>
       </c>
       <c r="E40">
-        <v>2043.986</v>
+        <v>2105.533</v>
       </c>
       <c r="F40">
-        <v>2338.786</v>
+        <v>2400.333</v>
       </c>
       <c r="G40">
         <v>173.9</v>
@@ -4689,37 +4689,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M40">
-        <v>469.6282288</v>
+        <v>481.9868664000001</v>
       </c>
       <c r="N40">
-        <v>-360.6119022693878</v>
+        <v>-372.9705398693878</v>
       </c>
       <c r="O40">
-        <v>-72.12238045387755</v>
+        <v>-74.59410797387757</v>
       </c>
       <c r="P40">
-        <v>-288.4895218155102</v>
+        <v>-298.3764318955103</v>
       </c>
       <c r="Q40">
-        <v>-221.6895218155102</v>
+        <v>-231.5764318955103</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.125444824911158</v>
+        <v>0.126750477778554</v>
       </c>
       <c r="T40">
-        <v>1.55242588035312</v>
+        <v>1.577875484949072</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.04642664978175275</v>
+        <v>0.0452362228642719</v>
       </c>
       <c r="W40">
-        <v>0.1914775287238241</v>
+        <v>0.1917165664488542</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2321332489087637</v>
+        <v>0.2261811143213595</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1520872523599711</v>
+        <v>0.1536372523599711</v>
       </c>
       <c r="C41">
-        <v>583.5761100830955</v>
+        <v>481.6394114834911</v>
       </c>
       <c r="D41">
-        <v>2810.009110083095</v>
+        <v>2769.619411483491</v>
       </c>
       <c r="E41">
-        <v>2105.533</v>
+        <v>2167.08</v>
       </c>
       <c r="F41">
-        <v>2400.333</v>
+        <v>2461.88</v>
       </c>
       <c r="G41">
         <v>173.9</v>
@@ -4771,37 +4771,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M41">
-        <v>481.9868664000001</v>
+        <v>494.3455040000001</v>
       </c>
       <c r="N41">
-        <v>-372.9705398693878</v>
+        <v>-385.3291774693878</v>
       </c>
       <c r="O41">
-        <v>-74.59410797387757</v>
+        <v>-77.06583549387756</v>
       </c>
       <c r="P41">
-        <v>-298.3764318955103</v>
+        <v>-308.2633419755102</v>
       </c>
       <c r="Q41">
-        <v>-231.5764318955103</v>
+        <v>-241.4633419755102</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.126750477778554</v>
+        <v>0.1280996524081966</v>
       </c>
       <c r="T41">
-        <v>1.577875484949072</v>
+        <v>1.604173409698224</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.0452362228642719</v>
+        <v>0.04410531729266511</v>
       </c>
       <c r="W41">
-        <v>0.1917165664488542</v>
+        <v>0.1919436522876329</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2261811143213595</v>
+        <v>0.2205265864633256</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1536372523599711</v>
+        <v>0.1551872523599711</v>
       </c>
       <c r="C42">
-        <v>481.6394114834911</v>
+        <v>380.8473441179417</v>
       </c>
       <c r="D42">
-        <v>2769.619411483491</v>
+        <v>2730.374344117942</v>
       </c>
       <c r="E42">
-        <v>2167.08</v>
+        <v>2228.627</v>
       </c>
       <c r="F42">
-        <v>2461.88</v>
+        <v>2523.427</v>
       </c>
       <c r="G42">
         <v>173.9</v>
@@ -4853,37 +4853,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M42">
-        <v>494.3455040000001</v>
+        <v>506.7041416000001</v>
       </c>
       <c r="N42">
-        <v>-385.3291774693878</v>
+        <v>-397.6878150693879</v>
       </c>
       <c r="O42">
-        <v>-77.06583549387756</v>
+        <v>-79.53756301387757</v>
       </c>
       <c r="P42">
-        <v>-308.2633419755102</v>
+        <v>-318.1502520555103</v>
       </c>
       <c r="Q42">
-        <v>-241.4633419755102</v>
+        <v>-251.3502520555103</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1280996524081966</v>
+        <v>0.1294945617710474</v>
       </c>
       <c r="T42">
-        <v>1.604173409698224</v>
+        <v>1.631362789523617</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.04410531729266511</v>
+        <v>0.04302957784650255</v>
       </c>
       <c r="W42">
-        <v>0.1919436522876329</v>
+        <v>0.1921596607684223</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2205265864633256</v>
+        <v>0.2151478892325126</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1551872523599711</v>
+        <v>0.1567372523599711</v>
       </c>
       <c r="C43">
-        <v>380.8473441179417</v>
+        <v>281.1519300969194</v>
       </c>
       <c r="D43">
-        <v>2730.374344117942</v>
+        <v>2692.225930096919</v>
       </c>
       <c r="E43">
-        <v>2228.627</v>
+        <v>2290.174</v>
       </c>
       <c r="F43">
-        <v>2523.427</v>
+        <v>2584.974</v>
       </c>
       <c r="G43">
         <v>173.9</v>
@@ -4935,37 +4935,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M43">
-        <v>506.7041416000001</v>
+        <v>519.0627792</v>
       </c>
       <c r="N43">
-        <v>-397.6878150693879</v>
+        <v>-410.0464526693878</v>
       </c>
       <c r="O43">
-        <v>-79.53756301387757</v>
+        <v>-82.00929053387756</v>
       </c>
       <c r="P43">
-        <v>-318.1502520555103</v>
+        <v>-328.0371621355102</v>
       </c>
       <c r="Q43">
-        <v>-251.3502520555103</v>
+        <v>-261.2371621355102</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1294945617710474</v>
+        <v>0.1309375714567551</v>
       </c>
       <c r="T43">
-        <v>1.631362789523617</v>
+        <v>1.659489734170576</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.04302957784650255</v>
+        <v>0.04200506408825249</v>
       </c>
       <c r="W43">
-        <v>0.1921596607684223</v>
+        <v>0.1923653831310789</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2151478892325126</v>
+        <v>0.2100253204412623</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1567372523599711</v>
+        <v>0.1582872523599711</v>
       </c>
       <c r="C44">
-        <v>281.1519300969198</v>
+        <v>182.5078359453414</v>
       </c>
       <c r="D44">
-        <v>2692.225930096919</v>
+        <v>2655.128835945341</v>
       </c>
       <c r="E44">
-        <v>2290.174</v>
+        <v>2351.721</v>
       </c>
       <c r="F44">
-        <v>2584.974</v>
+        <v>2646.521</v>
       </c>
       <c r="G44">
         <v>173.9</v>
@@ -5017,37 +5017,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M44">
-        <v>519.0627791999999</v>
+        <v>531.4214168</v>
       </c>
       <c r="N44">
-        <v>-410.0464526693877</v>
+        <v>-422.4050902693878</v>
       </c>
       <c r="O44">
-        <v>-82.00929053387755</v>
+        <v>-84.48101805387756</v>
       </c>
       <c r="P44">
-        <v>-328.0371621355101</v>
+        <v>-337.9240722155102</v>
       </c>
       <c r="Q44">
-        <v>-261.2371621355101</v>
+        <v>-271.1240722155102</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1309375714567551</v>
+        <v>0.1324312130612596</v>
       </c>
       <c r="T44">
-        <v>1.659489734170576</v>
+        <v>1.688603589156025</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.0420050640882525</v>
+        <v>0.04102820213271174</v>
       </c>
       <c r="W44">
-        <v>0.1923653831310789</v>
+        <v>0.1925615370117515</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2100253204412624</v>
+        <v>0.2051410106635586</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1582872523599711</v>
+        <v>0.1598372523599711</v>
       </c>
       <c r="C45">
-        <v>182.5078359453414</v>
+        <v>84.87219288750612</v>
       </c>
       <c r="D45">
-        <v>2655.128835945341</v>
+        <v>2619.040192887506</v>
       </c>
       <c r="E45">
-        <v>2351.721</v>
+        <v>2413.268</v>
       </c>
       <c r="F45">
-        <v>2646.521</v>
+        <v>2708.068</v>
       </c>
       <c r="G45">
         <v>173.9</v>
@@ -5099,37 +5099,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M45">
-        <v>531.4214168</v>
+        <v>543.7800543999999</v>
       </c>
       <c r="N45">
-        <v>-422.4050902693878</v>
+        <v>-434.7637278693877</v>
       </c>
       <c r="O45">
-        <v>-84.48101805387756</v>
+        <v>-86.95274557387755</v>
       </c>
       <c r="P45">
-        <v>-337.9240722155102</v>
+        <v>-347.8109822955101</v>
       </c>
       <c r="Q45">
-        <v>-271.1240722155102</v>
+        <v>-281.0109822955101</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1324312130612596</v>
+        <v>0.1339781990087821</v>
       </c>
       <c r="T45">
-        <v>1.688603589156025</v>
+        <v>1.718757224676668</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.04102820213271174</v>
+        <v>0.04009574299333193</v>
       </c>
       <c r="W45">
-        <v>0.1925615370117515</v>
+        <v>0.1927487748069389</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2051410106635586</v>
+        <v>0.2004787149666596</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1598372523599711</v>
+        <v>0.1772688823071041</v>
       </c>
       <c r="C46">
-        <v>84.87219288750612</v>
+        <v>-323.9367496947498</v>
       </c>
       <c r="D46">
-        <v>2619.040192887506</v>
+        <v>2271.77825030525</v>
       </c>
       <c r="E46">
-        <v>2413.268</v>
+        <v>2474.815</v>
       </c>
       <c r="F46">
-        <v>2708.068</v>
+        <v>2769.615</v>
       </c>
       <c r="G46">
         <v>173.9</v>
@@ -5181,45 +5181,45 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M46">
-        <v>543.7800543999999</v>
+        <v>653.075217</v>
       </c>
       <c r="N46">
-        <v>-434.7637278693877</v>
+        <v>-544.0588904693877</v>
       </c>
       <c r="O46">
-        <v>-86.95274557387755</v>
+        <v>-108.8117780938775</v>
       </c>
       <c r="P46">
-        <v>-347.8109822955101</v>
+        <v>-435.2471123755102</v>
       </c>
       <c r="Q46">
-        <v>-281.0109822955101</v>
+        <v>-368.4471123755102</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1339781990087821</v>
+        <v>0.1358207661673654</v>
       </c>
       <c r="T46">
-        <v>1.718757224676668</v>
+        <v>1.754672288165907</v>
       </c>
       <c r="U46">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04009574299333193</v>
+        <v>0.03338553468049064</v>
       </c>
       <c r="W46">
-        <v>0.1927487748069389</v>
+        <v>0.2279276909223403</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.2004787149666596</v>
+        <v>0.1669276734024532</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1772688823071041</v>
+        <v>0.1791688823071041</v>
       </c>
       <c r="C47">
-        <v>-323.9367496947498</v>
+        <v>-417.8479609028855</v>
       </c>
       <c r="D47">
-        <v>2271.77825030525</v>
+        <v>2239.414039097115</v>
       </c>
       <c r="E47">
-        <v>2474.815</v>
+        <v>2536.362</v>
       </c>
       <c r="F47">
-        <v>2769.615</v>
+        <v>2831.162</v>
       </c>
       <c r="G47">
         <v>173.9</v>
@@ -5263,37 +5263,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M47">
-        <v>653.075217</v>
+        <v>667.5879996000001</v>
       </c>
       <c r="N47">
-        <v>-544.0588904693877</v>
+        <v>-558.5716730693879</v>
       </c>
       <c r="O47">
-        <v>-108.8117780938775</v>
+        <v>-111.7143346138776</v>
       </c>
       <c r="P47">
-        <v>-435.2471123755102</v>
+        <v>-446.8573384555103</v>
       </c>
       <c r="Q47">
-        <v>-368.4471123755102</v>
+        <v>-380.0573384555103</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1358207661673654</v>
+        <v>0.137487817392687</v>
       </c>
       <c r="T47">
-        <v>1.754672288165907</v>
+        <v>1.787166219428239</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03338553468049064</v>
+        <v>0.03265976218743649</v>
       </c>
       <c r="W47">
-        <v>0.2279276909223403</v>
+        <v>0.2280988280762025</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1669276734024532</v>
+        <v>0.1632988109371823</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1791688823071041</v>
+        <v>0.1810688823071041</v>
       </c>
       <c r="C48">
-        <v>-417.8479609028855</v>
+        <v>-510.8499903354827</v>
       </c>
       <c r="D48">
-        <v>2239.414039097115</v>
+        <v>2207.959009664517</v>
       </c>
       <c r="E48">
-        <v>2536.362</v>
+        <v>2597.909</v>
       </c>
       <c r="F48">
-        <v>2831.162</v>
+        <v>2892.709</v>
       </c>
       <c r="G48">
         <v>173.9</v>
@@ -5345,37 +5345,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M48">
-        <v>667.5879996000001</v>
+        <v>682.1007822000001</v>
       </c>
       <c r="N48">
-        <v>-558.5716730693879</v>
+        <v>-573.0844556693879</v>
       </c>
       <c r="O48">
-        <v>-111.7143346138776</v>
+        <v>-114.6168911338776</v>
       </c>
       <c r="P48">
-        <v>-446.8573384555103</v>
+        <v>-458.4675645355103</v>
       </c>
       <c r="Q48">
-        <v>-380.0573384555103</v>
+        <v>-391.6675645355103</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.137487817392687</v>
+        <v>0.139217776211417</v>
       </c>
       <c r="T48">
-        <v>1.787166219428239</v>
+        <v>1.820886336775941</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03265976218743649</v>
+        <v>0.03196487363025699</v>
       </c>
       <c r="W48">
-        <v>0.2280988280762025</v>
+        <v>0.2282626827979854</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1632988109371823</v>
+        <v>0.1598243681512849</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1810688823071041</v>
+        <v>0.1829688823071041</v>
       </c>
       <c r="C49">
-        <v>-510.8499903354827</v>
+        <v>-602.9806186905653</v>
       </c>
       <c r="D49">
-        <v>2207.959009664517</v>
+        <v>2177.375381309435</v>
       </c>
       <c r="E49">
-        <v>2597.909</v>
+        <v>2659.456</v>
       </c>
       <c r="F49">
-        <v>2892.709</v>
+        <v>2954.256</v>
       </c>
       <c r="G49">
         <v>173.9</v>
@@ -5427,37 +5427,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M49">
-        <v>682.1007822000001</v>
+        <v>696.6135648000001</v>
       </c>
       <c r="N49">
-        <v>-573.0844556693879</v>
+        <v>-587.5972382693878</v>
       </c>
       <c r="O49">
-        <v>-114.6168911338776</v>
+        <v>-117.5194476538776</v>
       </c>
       <c r="P49">
-        <v>-458.4675645355103</v>
+        <v>-470.0777906155103</v>
       </c>
       <c r="Q49">
-        <v>-391.6675645355103</v>
+        <v>-403.2777906155102</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.139217776211417</v>
+        <v>0.1410142719077904</v>
       </c>
       <c r="T49">
-        <v>1.820886336775941</v>
+        <v>1.85590338171394</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03196487363025699</v>
+        <v>0.03129893876295997</v>
       </c>
       <c r="W49">
-        <v>0.2282626827979854</v>
+        <v>0.228419710239694</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1598243681512849</v>
+        <v>0.1564946938147999</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1829688823071041</v>
+        <v>0.1848688823071041</v>
       </c>
       <c r="C50">
-        <v>-602.9806186905648</v>
+        <v>-694.2755619820932</v>
       </c>
       <c r="D50">
-        <v>2177.375381309435</v>
+        <v>2147.627438017907</v>
       </c>
       <c r="E50">
-        <v>2659.456</v>
+        <v>2721.003</v>
       </c>
       <c r="F50">
-        <v>2954.256</v>
+        <v>3015.803</v>
       </c>
       <c r="G50">
         <v>173.9</v>
@@ -5509,37 +5509,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M50">
-        <v>696.6135647999999</v>
+        <v>711.1263474</v>
       </c>
       <c r="N50">
-        <v>-587.5972382693877</v>
+        <v>-602.1100208693878</v>
       </c>
       <c r="O50">
-        <v>-117.5194476538775</v>
+        <v>-120.4220041738776</v>
       </c>
       <c r="P50">
-        <v>-470.0777906155102</v>
+        <v>-481.6880166955102</v>
       </c>
       <c r="Q50">
-        <v>-403.2777906155102</v>
+        <v>-414.8880166955102</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1410142719077904</v>
+        <v>0.1428812184157862</v>
       </c>
       <c r="T50">
-        <v>1.85590338171394</v>
+        <v>1.892293644100488</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03129893876295998</v>
+        <v>0.03066018491065467</v>
       </c>
       <c r="W50">
-        <v>0.228419710239694</v>
+        <v>0.2285703283980676</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1564946938147999</v>
+        <v>0.1533009245532733</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1848688823071041</v>
+        <v>0.1867688823071041</v>
       </c>
       <c r="C51">
-        <v>-694.2755619820932</v>
+        <v>-784.76861068059</v>
       </c>
       <c r="D51">
-        <v>2147.627438017907</v>
+        <v>2118.68138931941</v>
       </c>
       <c r="E51">
-        <v>2721.003</v>
+        <v>2782.55</v>
       </c>
       <c r="F51">
-        <v>3015.803</v>
+        <v>3077.35</v>
       </c>
       <c r="G51">
         <v>173.9</v>
@@ -5591,37 +5591,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M51">
-        <v>711.1263474</v>
+        <v>725.63913</v>
       </c>
       <c r="N51">
-        <v>-602.1100208693878</v>
+        <v>-616.6228034693878</v>
       </c>
       <c r="O51">
-        <v>-120.4220041738776</v>
+        <v>-123.3245606938776</v>
       </c>
       <c r="P51">
-        <v>-481.6880166955102</v>
+        <v>-493.2982427755102</v>
       </c>
       <c r="Q51">
-        <v>-414.8880166955102</v>
+        <v>-426.4982427755102</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1428812184157862</v>
+        <v>0.144822842784102</v>
       </c>
       <c r="T51">
-        <v>1.892293644100488</v>
+        <v>1.930139516982498</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03066018491065467</v>
+        <v>0.03004698121244158</v>
       </c>
       <c r="W51">
-        <v>0.2285703283980676</v>
+        <v>0.2287149218301063</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1533009245532733</v>
+        <v>0.1502349060622078</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1867688823071041</v>
+        <v>0.1886688823071042</v>
       </c>
       <c r="C52">
-        <v>-784.76861068059</v>
+        <v>-874.491757751257</v>
       </c>
       <c r="D52">
-        <v>2118.68138931941</v>
+        <v>2090.505242248743</v>
       </c>
       <c r="E52">
-        <v>2782.55</v>
+        <v>2844.097</v>
       </c>
       <c r="F52">
-        <v>3077.35</v>
+        <v>3138.897</v>
       </c>
       <c r="G52">
         <v>173.9</v>
@@ -5673,37 +5673,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M52">
-        <v>725.63913</v>
+        <v>740.1519126000001</v>
       </c>
       <c r="N52">
-        <v>-616.6228034693878</v>
+        <v>-631.1355860693878</v>
       </c>
       <c r="O52">
-        <v>-123.3245606938776</v>
+        <v>-126.2271172138776</v>
       </c>
       <c r="P52">
-        <v>-493.2982427755102</v>
+        <v>-504.9084688555103</v>
       </c>
       <c r="Q52">
-        <v>-426.4982427755102</v>
+        <v>-438.1084688555102</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.144822842784102</v>
+        <v>0.1468437171266347</v>
       </c>
       <c r="T52">
-        <v>1.930139516982498</v>
+        <v>1.969530119369896</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03004698121244158</v>
+        <v>0.02945782471807997</v>
       </c>
       <c r="W52">
-        <v>0.2287149218301063</v>
+        <v>0.2288538449314768</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1502349060622078</v>
+        <v>0.1472891235903998</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1886688823071042</v>
+        <v>0.1905688823071041</v>
       </c>
       <c r="C53">
-        <v>-874.491757751257</v>
+        <v>-963.4753166095807</v>
       </c>
       <c r="D53">
-        <v>2090.505242248743</v>
+        <v>2063.068683390419</v>
       </c>
       <c r="E53">
-        <v>2844.097</v>
+        <v>2905.644</v>
       </c>
       <c r="F53">
-        <v>3138.897</v>
+        <v>3200.444</v>
       </c>
       <c r="G53">
         <v>173.9</v>
@@ -5755,37 +5755,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M53">
-        <v>740.1519126000001</v>
+        <v>754.6646952</v>
       </c>
       <c r="N53">
-        <v>-631.1355860693878</v>
+        <v>-645.6483686693878</v>
       </c>
       <c r="O53">
-        <v>-126.2271172138776</v>
+        <v>-129.1296737338776</v>
       </c>
       <c r="P53">
-        <v>-504.9084688555103</v>
+        <v>-516.5186949355102</v>
       </c>
       <c r="Q53">
-        <v>-438.1084688555102</v>
+        <v>-449.7186949355102</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1468437171266347</v>
+        <v>0.1489487945667729</v>
       </c>
       <c r="T53">
-        <v>1.969530119369896</v>
+        <v>2.010561996856768</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02945782471807997</v>
+        <v>0.02889132808888613</v>
       </c>
       <c r="W53">
-        <v>0.2288538449314768</v>
+        <v>0.2289874248366406</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1472891235903998</v>
+        <v>0.1444566404444306</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1905688823071041</v>
+        <v>0.1924688823071042</v>
       </c>
       <c r="C54">
-        <v>-963.4753166095807</v>
+        <v>-1051.7480299087</v>
       </c>
       <c r="D54">
-        <v>2063.068683390419</v>
+        <v>2036.3429700913</v>
       </c>
       <c r="E54">
-        <v>2905.644</v>
+        <v>2967.191</v>
       </c>
       <c r="F54">
-        <v>3200.444</v>
+        <v>3261.991</v>
       </c>
       <c r="G54">
         <v>173.9</v>
@@ -5837,37 +5837,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M54">
-        <v>754.6646952</v>
+        <v>769.1774778</v>
       </c>
       <c r="N54">
-        <v>-645.6483686693878</v>
+        <v>-660.1611512693878</v>
       </c>
       <c r="O54">
-        <v>-129.1296737338776</v>
+        <v>-132.0322302538776</v>
       </c>
       <c r="P54">
-        <v>-516.5186949355102</v>
+        <v>-528.1289210155103</v>
       </c>
       <c r="Q54">
-        <v>-449.7186949355102</v>
+        <v>-461.3289210155103</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1489487945667729</v>
+        <v>0.1511434497703213</v>
       </c>
       <c r="T54">
-        <v>2.010561996856768</v>
+        <v>2.053339911683508</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02889132808888613</v>
+        <v>0.02834620869098262</v>
       </c>
       <c r="W54">
-        <v>0.2289874248366406</v>
+        <v>0.2291159639906663</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1444566404444306</v>
+        <v>0.1417310434549131</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1924688823071042</v>
+        <v>0.1943688823071041</v>
       </c>
       <c r="C55">
-        <v>-1051.7480299087</v>
+        <v>-1139.337169979295</v>
       </c>
       <c r="D55">
-        <v>2036.3429700913</v>
+        <v>2010.300830020705</v>
       </c>
       <c r="E55">
-        <v>2967.191</v>
+        <v>3028.738</v>
       </c>
       <c r="F55">
-        <v>3261.991</v>
+        <v>3323.538</v>
       </c>
       <c r="G55">
         <v>173.9</v>
@@ -5919,37 +5919,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M55">
-        <v>769.1774778</v>
+        <v>783.6902604000001</v>
       </c>
       <c r="N55">
-        <v>-660.1611512693878</v>
+        <v>-674.6739338693878</v>
       </c>
       <c r="O55">
-        <v>-132.0322302538776</v>
+        <v>-134.9347867738776</v>
       </c>
       <c r="P55">
-        <v>-528.1289210155103</v>
+        <v>-539.7391470955102</v>
       </c>
       <c r="Q55">
-        <v>-461.3289210155103</v>
+        <v>-472.9391470955102</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1511434497703213</v>
+        <v>0.1534335247653282</v>
       </c>
       <c r="T55">
-        <v>2.053339911683508</v>
+        <v>2.097977735850541</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02834620869098262</v>
+        <v>0.02782127890040886</v>
       </c>
       <c r="W55">
-        <v>0.2291159639906663</v>
+        <v>0.2292397424352836</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1417310434549131</v>
+        <v>0.1391063945020443</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1943688823071041</v>
+        <v>0.1962688823071042</v>
       </c>
       <c r="C56">
-        <v>-1139.337169979295</v>
+        <v>-1226.268631659842</v>
       </c>
       <c r="D56">
-        <v>2010.300830020705</v>
+        <v>1984.916368340158</v>
       </c>
       <c r="E56">
-        <v>3028.738</v>
+        <v>3090.285</v>
       </c>
       <c r="F56">
-        <v>3323.538</v>
+        <v>3385.085</v>
       </c>
       <c r="G56">
         <v>173.9</v>
@@ -6001,37 +6001,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M56">
-        <v>783.6902604000001</v>
+        <v>798.2030430000001</v>
       </c>
       <c r="N56">
-        <v>-674.6739338693878</v>
+        <v>-689.1867164693879</v>
       </c>
       <c r="O56">
-        <v>-134.9347867738776</v>
+        <v>-137.8373432938776</v>
       </c>
       <c r="P56">
-        <v>-539.7391470955102</v>
+        <v>-551.3493731755103</v>
       </c>
       <c r="Q56">
-        <v>-472.9391470955102</v>
+        <v>-484.5493731755103</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1534335247653282</v>
+        <v>0.1558253808712245</v>
       </c>
       <c r="T56">
-        <v>2.097977735850541</v>
+        <v>2.144599463313887</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02782127890040886</v>
+        <v>0.02731543746585598</v>
       </c>
       <c r="W56">
-        <v>0.2292397424352836</v>
+        <v>0.2293590198455512</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1391063945020443</v>
+        <v>0.1365771873292798</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1962688823071042</v>
+        <v>0.1981688823071041</v>
       </c>
       <c r="C57">
-        <v>-1226.268631659842</v>
+        <v>-1312.567018181435</v>
       </c>
       <c r="D57">
-        <v>1984.916368340158</v>
+        <v>1960.164981818565</v>
       </c>
       <c r="E57">
-        <v>3090.285</v>
+        <v>3151.832</v>
       </c>
       <c r="F57">
-        <v>3385.085</v>
+        <v>3446.632</v>
       </c>
       <c r="G57">
         <v>173.9</v>
@@ -6083,37 +6083,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M57">
-        <v>798.2030430000001</v>
+        <v>812.7158256</v>
       </c>
       <c r="N57">
-        <v>-689.1867164693879</v>
+        <v>-703.6994990693878</v>
       </c>
       <c r="O57">
-        <v>-137.8373432938776</v>
+        <v>-140.7398998138776</v>
       </c>
       <c r="P57">
-        <v>-551.3493731755103</v>
+        <v>-562.9595992555103</v>
       </c>
       <c r="Q57">
-        <v>-484.5493731755103</v>
+        <v>-496.1595992555103</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1558253808712245</v>
+        <v>0.1583259577092068</v>
       </c>
       <c r="T57">
-        <v>2.144599463313887</v>
+        <v>2.193340360207384</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02731543746585598</v>
+        <v>0.02682766179682283</v>
       </c>
       <c r="W57">
-        <v>0.2293590198455512</v>
+        <v>0.2294740373483092</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1365771873292798</v>
+        <v>0.1341383089841142</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1981688823071041</v>
+        <v>0.2000688823071042</v>
       </c>
       <c r="C58">
-        <v>-1312.567018181435</v>
+        <v>-1398.255720706</v>
       </c>
       <c r="D58">
-        <v>1960.164981818565</v>
+        <v>1936.023279294</v>
       </c>
       <c r="E58">
-        <v>3151.832</v>
+        <v>3213.379</v>
       </c>
       <c r="F58">
-        <v>3446.632</v>
+        <v>3508.179</v>
       </c>
       <c r="G58">
         <v>173.9</v>
@@ -6165,37 +6165,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M58">
-        <v>812.7158256</v>
+        <v>827.2286082000001</v>
       </c>
       <c r="N58">
-        <v>-703.6994990693878</v>
+        <v>-718.2122816693878</v>
       </c>
       <c r="O58">
-        <v>-140.7398998138776</v>
+        <v>-143.6424563338776</v>
       </c>
       <c r="P58">
-        <v>-562.9595992555103</v>
+        <v>-574.5698253355102</v>
       </c>
       <c r="Q58">
-        <v>-496.1595992555103</v>
+        <v>-507.7698253355102</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1583259577092068</v>
+        <v>0.1609428404466302</v>
       </c>
       <c r="T58">
-        <v>2.193340360207384</v>
+        <v>2.244348275561044</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02682766179682283</v>
+        <v>0.02635700106354524</v>
       </c>
       <c r="W58">
-        <v>0.2294740373483092</v>
+        <v>0.2295850191492161</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1341383089841142</v>
+        <v>0.1317850053177262</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2000688823071042</v>
+        <v>0.2019688823071041</v>
       </c>
       <c r="C59">
-        <v>-1398.255720706</v>
+        <v>-1483.356992058375</v>
       </c>
       <c r="D59">
-        <v>1936.023279294</v>
+        <v>1912.469007941625</v>
       </c>
       <c r="E59">
-        <v>3213.379</v>
+        <v>3274.926</v>
       </c>
       <c r="F59">
-        <v>3508.179</v>
+        <v>3569.726</v>
       </c>
       <c r="G59">
         <v>173.9</v>
@@ -6247,37 +6247,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M59">
-        <v>827.2286082000001</v>
+        <v>841.7413908000001</v>
       </c>
       <c r="N59">
-        <v>-718.2122816693878</v>
+        <v>-732.7250642693879</v>
       </c>
       <c r="O59">
-        <v>-143.6424563338776</v>
+        <v>-146.5450128538776</v>
       </c>
       <c r="P59">
-        <v>-574.5698253355102</v>
+        <v>-586.1800514155103</v>
       </c>
       <c r="Q59">
-        <v>-507.7698253355102</v>
+        <v>-519.3800514155103</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1609428404466302</v>
+        <v>0.1636843366477405</v>
       </c>
       <c r="T59">
-        <v>2.244348275561044</v>
+        <v>2.297785139264878</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02635700106354524</v>
+        <v>0.0259025700107255</v>
       </c>
       <c r="W59">
-        <v>0.2295850191492161</v>
+        <v>0.2296921739914709</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1317850053177262</v>
+        <v>0.1295128500536274</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2019688823071041</v>
+        <v>0.2038688823071041</v>
       </c>
       <c r="C60">
-        <v>-1483.356992058375</v>
+        <v>-1567.892015140801</v>
       </c>
       <c r="D60">
-        <v>1912.469007941625</v>
+        <v>1889.480984859199</v>
       </c>
       <c r="E60">
-        <v>3274.925999999999</v>
+        <v>3336.473</v>
       </c>
       <c r="F60">
-        <v>3569.726</v>
+        <v>3631.273</v>
       </c>
       <c r="G60">
         <v>173.9</v>
@@ -6329,37 +6329,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M60">
-        <v>841.7413908</v>
+        <v>856.2541734</v>
       </c>
       <c r="N60">
-        <v>-732.7250642693878</v>
+        <v>-747.2378468693878</v>
       </c>
       <c r="O60">
-        <v>-146.5450128538776</v>
+        <v>-149.4475693738776</v>
       </c>
       <c r="P60">
-        <v>-586.1800514155102</v>
+        <v>-597.7902774955103</v>
       </c>
       <c r="Q60">
-        <v>-519.3800514155103</v>
+        <v>-530.9902774955103</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1636843366477404</v>
+        <v>0.1665595643708561</v>
       </c>
       <c r="T60">
-        <v>2.297785139264878</v>
+        <v>2.353828679246948</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0259025700107255</v>
+        <v>0.02546354340037422</v>
       </c>
       <c r="W60">
-        <v>0.2296921739914709</v>
+        <v>0.2297956964661917</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1295128500536274</v>
+        <v>0.127317717001871</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2038688823071041</v>
+        <v>0.2057688823071041</v>
       </c>
       <c r="C61">
-        <v>-1567.892015140801</v>
+        <v>-1651.880966471938</v>
       </c>
       <c r="D61">
-        <v>1889.480984859199</v>
+        <v>1867.039033528062</v>
       </c>
       <c r="E61">
-        <v>3336.473</v>
+        <v>3398.02</v>
       </c>
       <c r="F61">
-        <v>3631.273</v>
+        <v>3692.82</v>
       </c>
       <c r="G61">
         <v>173.9</v>
@@ -6411,37 +6411,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M61">
-        <v>856.2541734</v>
+        <v>870.7669559999999</v>
       </c>
       <c r="N61">
-        <v>-747.2378468693878</v>
+        <v>-761.7506294693877</v>
       </c>
       <c r="O61">
-        <v>-149.4475693738776</v>
+        <v>-152.3501258938776</v>
       </c>
       <c r="P61">
-        <v>-597.7902774955103</v>
+        <v>-609.4005035755101</v>
       </c>
       <c r="Q61">
-        <v>-530.9902774955103</v>
+        <v>-542.6005035755102</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1665595643708561</v>
+        <v>0.1695785534801275</v>
       </c>
       <c r="T61">
-        <v>2.353828679246948</v>
+        <v>2.412674396228121</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02546354340037422</v>
+        <v>0.02503915101036798</v>
       </c>
       <c r="W61">
-        <v>0.2297956964661917</v>
+        <v>0.2298957681917552</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.127317717001871</v>
+        <v>0.1251957550518399</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2057688823071041</v>
+        <v>0.2076688823071041</v>
       </c>
       <c r="C62">
-        <v>-1651.880966471938</v>
+        <v>-1735.343075250987</v>
       </c>
       <c r="D62">
-        <v>1867.039033528062</v>
+        <v>1845.123924749012</v>
       </c>
       <c r="E62">
-        <v>3398.02</v>
+        <v>3459.567</v>
       </c>
       <c r="F62">
-        <v>3692.82</v>
+        <v>3754.367</v>
       </c>
       <c r="G62">
         <v>173.9</v>
@@ -6493,37 +6493,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M62">
-        <v>870.7669559999999</v>
+        <v>885.2797386</v>
       </c>
       <c r="N62">
-        <v>-761.7506294693877</v>
+        <v>-776.2634120693878</v>
       </c>
       <c r="O62">
-        <v>-152.3501258938776</v>
+        <v>-155.2526824138776</v>
       </c>
       <c r="P62">
-        <v>-609.4005035755101</v>
+        <v>-621.0107296555102</v>
       </c>
       <c r="Q62">
-        <v>-542.6005035755102</v>
+        <v>-554.2107296555102</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1695785534801275</v>
+        <v>0.1727523625437205</v>
       </c>
       <c r="T62">
-        <v>2.412674396228121</v>
+        <v>2.474537842285253</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02503915101036798</v>
+        <v>0.02462867312495211</v>
       </c>
       <c r="W62">
-        <v>0.2298957681917552</v>
+        <v>0.2299925588771363</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1251957550518399</v>
+        <v>0.1231433656247605</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2076688823071041</v>
+        <v>0.2095688823071041</v>
       </c>
       <c r="C63">
-        <v>-1735.343075250987</v>
+        <v>-1818.296678310347</v>
       </c>
       <c r="D63">
-        <v>1845.123924749012</v>
+        <v>1823.717321689652</v>
       </c>
       <c r="E63">
-        <v>3459.567</v>
+        <v>3521.114</v>
       </c>
       <c r="F63">
-        <v>3754.367</v>
+        <v>3815.914</v>
       </c>
       <c r="G63">
         <v>173.9</v>
@@ -6575,37 +6575,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M63">
-        <v>885.2797386</v>
+        <v>899.7925212</v>
       </c>
       <c r="N63">
-        <v>-776.2634120693878</v>
+        <v>-790.7761946693878</v>
       </c>
       <c r="O63">
-        <v>-155.2526824138776</v>
+        <v>-158.1552389338776</v>
       </c>
       <c r="P63">
-        <v>-621.0107296555102</v>
+        <v>-632.6209557355103</v>
       </c>
       <c r="Q63">
-        <v>-554.2107296555102</v>
+        <v>-565.8209557355103</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1727523625437205</v>
+        <v>0.1760932141896079</v>
       </c>
       <c r="T63">
-        <v>2.474537842285253</v>
+        <v>2.539657259187497</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02462867312495211</v>
+        <v>0.02423143646164643</v>
       </c>
       <c r="W63">
-        <v>0.2299925588771363</v>
+        <v>0.2300862272823438</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1231433656247605</v>
+        <v>0.1211571823082321</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2095688823071041</v>
+        <v>0.2114688823071041</v>
       </c>
       <c r="C64">
-        <v>-1818.296678310347</v>
+        <v>-1900.759271286867</v>
       </c>
       <c r="D64">
-        <v>1823.717321689652</v>
+        <v>1802.801728713133</v>
       </c>
       <c r="E64">
-        <v>3521.114</v>
+        <v>3582.661</v>
       </c>
       <c r="F64">
-        <v>3815.914</v>
+        <v>3877.461</v>
       </c>
       <c r="G64">
         <v>173.9</v>
@@ -6657,37 +6657,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M64">
-        <v>899.7925212</v>
+        <v>914.3053037999999</v>
       </c>
       <c r="N64">
-        <v>-790.7761946693878</v>
+        <v>-805.2889772693877</v>
       </c>
       <c r="O64">
-        <v>-158.1552389338776</v>
+        <v>-161.0577954538776</v>
       </c>
       <c r="P64">
-        <v>-632.6209557355103</v>
+        <v>-644.2311818155101</v>
       </c>
       <c r="Q64">
-        <v>-565.8209557355103</v>
+        <v>-577.4311818155102</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1760932141896079</v>
+        <v>0.1796146524109486</v>
       </c>
       <c r="T64">
-        <v>2.539657259187497</v>
+        <v>2.608296644570943</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02423143646164643</v>
+        <v>0.02384681048606474</v>
       </c>
       <c r="W64">
-        <v>0.2300862272823438</v>
+        <v>0.2301769220873859</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1211571823082321</v>
+        <v>0.1192340524303237</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2114688823071041</v>
+        <v>0.2133688823071041</v>
       </c>
       <c r="C65">
-        <v>-1900.759271286867</v>
+        <v>-1982.747556311836</v>
       </c>
       <c r="D65">
-        <v>1802.801728713133</v>
+        <v>1782.360443688164</v>
       </c>
       <c r="E65">
-        <v>3582.661</v>
+        <v>3644.208</v>
       </c>
       <c r="F65">
-        <v>3877.461</v>
+        <v>3939.008</v>
       </c>
       <c r="G65">
         <v>173.9</v>
@@ -6739,37 +6739,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M65">
-        <v>914.3053037999999</v>
+        <v>928.8180864</v>
       </c>
       <c r="N65">
-        <v>-805.2889772693877</v>
+        <v>-819.8017598693878</v>
       </c>
       <c r="O65">
-        <v>-161.0577954538776</v>
+        <v>-163.9603519738776</v>
       </c>
       <c r="P65">
-        <v>-644.2311818155101</v>
+        <v>-655.8414078955102</v>
       </c>
       <c r="Q65">
-        <v>-577.4311818155102</v>
+        <v>-589.0414078955102</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1796146524109486</v>
+        <v>0.1833317260890306</v>
       </c>
       <c r="T65">
-        <v>2.608296644570943</v>
+        <v>2.680749329142358</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02384681048606474</v>
+        <v>0.02347420407221998</v>
       </c>
       <c r="W65">
-        <v>0.2301769220873859</v>
+        <v>0.2302647826797705</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1192340524303237</v>
+        <v>0.1173710203610999</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2133688823071041</v>
+        <v>0.2152688823071041</v>
       </c>
       <c r="C66">
-        <v>-1982.747556311836</v>
+        <v>-2064.27748649291</v>
       </c>
       <c r="D66">
-        <v>1782.360443688164</v>
+        <v>1762.37751350709</v>
       </c>
       <c r="E66">
-        <v>3644.208</v>
+        <v>3705.755</v>
       </c>
       <c r="F66">
-        <v>3939.008</v>
+        <v>4000.555</v>
       </c>
       <c r="G66">
         <v>173.9</v>
@@ -6821,37 +6821,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M66">
-        <v>928.8180864</v>
+        <v>943.330869</v>
       </c>
       <c r="N66">
-        <v>-819.8017598693878</v>
+        <v>-834.3145424693878</v>
       </c>
       <c r="O66">
-        <v>-163.9603519738776</v>
+        <v>-166.8629084938776</v>
       </c>
       <c r="P66">
-        <v>-655.8414078955102</v>
+        <v>-667.4516339755103</v>
       </c>
       <c r="Q66">
-        <v>-589.0414078955102</v>
+        <v>-600.6516339755103</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1833317260890306</v>
+        <v>0.1872612039772886</v>
       </c>
       <c r="T66">
-        <v>2.680749329142358</v>
+        <v>2.757342167117854</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02347420407221998</v>
+        <v>0.02311306247110891</v>
       </c>
       <c r="W66">
-        <v>0.2302647826797705</v>
+        <v>0.2303499398693125</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1173710203610999</v>
+        <v>0.1155653123555445</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2152688823071041</v>
+        <v>0.2171688823071041</v>
       </c>
       <c r="C67">
-        <v>-2064.27748649291</v>
+        <v>-2145.364307436964</v>
       </c>
       <c r="D67">
-        <v>1762.37751350709</v>
+        <v>1742.837692563036</v>
       </c>
       <c r="E67">
-        <v>3705.755</v>
+        <v>3767.302</v>
       </c>
       <c r="F67">
-        <v>4000.555</v>
+        <v>4062.102</v>
       </c>
       <c r="G67">
         <v>173.9</v>
@@ -6903,37 +6903,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M67">
-        <v>943.330869</v>
+        <v>957.8436516</v>
       </c>
       <c r="N67">
-        <v>-834.3145424693878</v>
+        <v>-848.8273250693878</v>
       </c>
       <c r="O67">
-        <v>-166.8629084938776</v>
+        <v>-169.7654650138776</v>
       </c>
       <c r="P67">
-        <v>-667.4516339755103</v>
+        <v>-679.0618600555102</v>
       </c>
       <c r="Q67">
-        <v>-600.6516339755103</v>
+        <v>-612.2618600555102</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1872612039772886</v>
+        <v>0.1914218276236794</v>
       </c>
       <c r="T67">
-        <v>2.757342167117854</v>
+        <v>2.838440466150732</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02311306247110891</v>
+        <v>0.02276286455487998</v>
       </c>
       <c r="W67">
-        <v>0.2303499398693125</v>
+        <v>0.2304325165379593</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1155653123555445</v>
+        <v>0.1138143227743998</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2171688823071041</v>
+        <v>0.2190688823071041</v>
       </c>
       <c r="C68">
-        <v>-2145.364307436964</v>
+        <v>-2226.022596041</v>
       </c>
       <c r="D68">
-        <v>1742.837692563036</v>
+        <v>1723.726403959</v>
       </c>
       <c r="E68">
-        <v>3767.302</v>
+        <v>3828.849</v>
       </c>
       <c r="F68">
-        <v>4062.102</v>
+        <v>4123.649</v>
       </c>
       <c r="G68">
         <v>173.9</v>
@@ -6985,37 +6985,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M68">
-        <v>957.8436516</v>
+        <v>972.3564342000001</v>
       </c>
       <c r="N68">
-        <v>-848.8273250693878</v>
+        <v>-863.3401076693879</v>
       </c>
       <c r="O68">
-        <v>-169.7654650138776</v>
+        <v>-172.6680215338776</v>
       </c>
       <c r="P68">
-        <v>-679.0618600555102</v>
+        <v>-690.6720861355103</v>
       </c>
       <c r="Q68">
-        <v>-612.2618600555102</v>
+        <v>-623.8720861355102</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1914218276236794</v>
+        <v>0.1958346102789424</v>
       </c>
       <c r="T68">
-        <v>2.838440466150732</v>
+        <v>2.924453813609845</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02276286455487998</v>
+        <v>0.02242312030779222</v>
       </c>
       <c r="W68">
-        <v>0.2304325165379593</v>
+        <v>0.2305126282314226</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1138143227743998</v>
+        <v>0.1121156015389611</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2190688823071041</v>
+        <v>0.2209688823071042</v>
       </c>
       <c r="C69">
-        <v>-2226.022596041</v>
+        <v>-2306.266296758542</v>
       </c>
       <c r="D69">
-        <v>1723.726403959</v>
+        <v>1705.029703241458</v>
       </c>
       <c r="E69">
-        <v>3828.849</v>
+        <v>3890.396</v>
       </c>
       <c r="F69">
-        <v>4123.649</v>
+        <v>4185.196</v>
       </c>
       <c r="G69">
         <v>173.9</v>
@@ -7067,37 +7067,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M69">
-        <v>972.3564342000001</v>
+        <v>986.8692168</v>
       </c>
       <c r="N69">
-        <v>-863.3401076693879</v>
+        <v>-877.8528902693878</v>
       </c>
       <c r="O69">
-        <v>-172.6680215338776</v>
+        <v>-175.5705780538776</v>
       </c>
       <c r="P69">
-        <v>-690.6720861355103</v>
+        <v>-702.2823122155103</v>
       </c>
       <c r="Q69">
-        <v>-623.8720861355102</v>
+        <v>-635.4823122155103</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1958346102789424</v>
+        <v>0.2005231918501594</v>
       </c>
       <c r="T69">
-        <v>2.924453813609845</v>
+        <v>3.015842995285153</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02242312030779222</v>
+        <v>0.02209336853855998</v>
       </c>
       <c r="W69">
-        <v>0.2305126282314226</v>
+        <v>0.2305903836986075</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1121156015389611</v>
+        <v>0.1104668426927998</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2209688823071042</v>
+        <v>0.2228688823071041</v>
       </c>
       <c r="C70">
-        <v>-2306.266296758542</v>
+        <v>-2386.108755531134</v>
       </c>
       <c r="D70">
-        <v>1705.029703241458</v>
+        <v>1686.734244468866</v>
       </c>
       <c r="E70">
-        <v>3890.396</v>
+        <v>3951.943</v>
       </c>
       <c r="F70">
-        <v>4185.196</v>
+        <v>4246.743</v>
       </c>
       <c r="G70">
         <v>173.9</v>
@@ -7149,37 +7149,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M70">
-        <v>986.8692168</v>
+        <v>1001.3819994</v>
       </c>
       <c r="N70">
-        <v>-877.8528902693878</v>
+        <v>-892.3656728693879</v>
       </c>
       <c r="O70">
-        <v>-175.5705780538776</v>
+        <v>-178.4731345738776</v>
       </c>
       <c r="P70">
-        <v>-702.2823122155103</v>
+        <v>-713.8925382955103</v>
       </c>
       <c r="Q70">
-        <v>-635.4823122155103</v>
+        <v>-647.0925382955104</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2005231918501594</v>
+        <v>0.2055142625550032</v>
       </c>
       <c r="T70">
-        <v>3.015842995285153</v>
+        <v>3.113128253197577</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02209336853855998</v>
+        <v>0.02177317479162433</v>
       </c>
       <c r="W70">
-        <v>0.2305903836986075</v>
+        <v>0.230665885384135</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1104668426927998</v>
+        <v>0.1088658739581216</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2228688823071041</v>
+        <v>0.2247688823071041</v>
       </c>
       <c r="C71">
-        <v>-2386.108755531134</v>
+        <v>-2465.562751558475</v>
       </c>
       <c r="D71">
-        <v>1686.734244468866</v>
+        <v>1668.827248441525</v>
       </c>
       <c r="E71">
-        <v>3951.943</v>
+        <v>4013.49</v>
       </c>
       <c r="F71">
-        <v>4246.743</v>
+        <v>4308.29</v>
       </c>
       <c r="G71">
         <v>173.9</v>
@@ -7231,37 +7231,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M71">
-        <v>1001.3819994</v>
+        <v>1015.894782</v>
       </c>
       <c r="N71">
-        <v>-892.3656728693879</v>
+        <v>-906.8784554693879</v>
       </c>
       <c r="O71">
-        <v>-178.4731345738776</v>
+        <v>-181.3756910938776</v>
       </c>
       <c r="P71">
-        <v>-713.8925382955103</v>
+        <v>-725.5027643755103</v>
       </c>
       <c r="Q71">
-        <v>-647.0925382955104</v>
+        <v>-658.7027643755102</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2055142625550032</v>
+        <v>0.2108380713068367</v>
       </c>
       <c r="T71">
-        <v>3.113128253197577</v>
+        <v>3.21689919497083</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02177317479162433</v>
+        <v>0.02146212943745827</v>
       </c>
       <c r="W71">
-        <v>0.230665885384135</v>
+        <v>0.2307392298786473</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1088658739581216</v>
+        <v>0.1073106471872913</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2247688823071041</v>
+        <v>0.2266688823071042</v>
       </c>
       <c r="C72">
-        <v>-2465.562751558475</v>
+        <v>-2544.640527066088</v>
       </c>
       <c r="D72">
-        <v>1668.827248441525</v>
+        <v>1651.296472933912</v>
       </c>
       <c r="E72">
-        <v>4013.49</v>
+        <v>4075.037</v>
       </c>
       <c r="F72">
-        <v>4308.29</v>
+        <v>4369.837</v>
       </c>
       <c r="G72">
         <v>173.9</v>
@@ -7313,37 +7313,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M72">
-        <v>1015.894782</v>
+        <v>1030.4075646</v>
       </c>
       <c r="N72">
-        <v>-906.8784554693879</v>
+        <v>-921.3912380693879</v>
       </c>
       <c r="O72">
-        <v>-181.3756910938776</v>
+        <v>-184.2782476138776</v>
       </c>
       <c r="P72">
-        <v>-725.5027643755103</v>
+        <v>-737.1129904555103</v>
       </c>
       <c r="Q72">
-        <v>-658.7027643755102</v>
+        <v>-670.3129904555103</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2108380713068367</v>
+        <v>0.2165290392829345</v>
       </c>
       <c r="T72">
-        <v>3.21689919497083</v>
+        <v>3.3278267534181</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02146212943745827</v>
+        <v>0.02115984592425463</v>
       </c>
       <c r="W72">
-        <v>0.2307392298786473</v>
+        <v>0.2308105083310608</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1073106471872913</v>
+        <v>0.1057992296212731</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2266688823071041</v>
+        <v>0.2285688823071041</v>
       </c>
       <c r="C73">
-        <v>-2544.640527066088</v>
+        <v>-2623.353815216292</v>
       </c>
       <c r="D73">
-        <v>1651.296472933911</v>
+        <v>1634.130184783708</v>
       </c>
       <c r="E73">
-        <v>4075.036999999999</v>
+        <v>4136.584</v>
       </c>
       <c r="F73">
-        <v>4369.837</v>
+        <v>4431.384</v>
       </c>
       <c r="G73">
         <v>173.9</v>
@@ -7395,37 +7395,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M73">
-        <v>1030.4075646</v>
+        <v>1044.9203472</v>
       </c>
       <c r="N73">
-        <v>-921.3912380693877</v>
+        <v>-935.9040206693879</v>
       </c>
       <c r="O73">
-        <v>-184.2782476138775</v>
+        <v>-187.1808041338776</v>
       </c>
       <c r="P73">
-        <v>-737.1129904555102</v>
+        <v>-748.7232165355103</v>
       </c>
       <c r="Q73">
-        <v>-670.3129904555101</v>
+        <v>-681.9232165355104</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2165290392829344</v>
+        <v>0.2226265049716107</v>
       </c>
       <c r="T73">
-        <v>3.327826753418099</v>
+        <v>3.446677708897317</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02115984592425463</v>
+        <v>0.02086595917530665</v>
       </c>
       <c r="W73">
-        <v>0.2308105083310608</v>
+        <v>0.2308798068264627</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1057992296212731</v>
+        <v>0.1043297958765332</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2285688823071041</v>
+        <v>0.2304688823071041</v>
       </c>
       <c r="C74">
-        <v>-2623.353815216292</v>
+        <v>-2701.713866296146</v>
       </c>
       <c r="D74">
-        <v>1634.130184783708</v>
+        <v>1617.317133703853</v>
       </c>
       <c r="E74">
-        <v>4136.584</v>
+        <v>4198.130999999999</v>
       </c>
       <c r="F74">
-        <v>4431.384</v>
+        <v>4492.931</v>
       </c>
       <c r="G74">
         <v>173.9</v>
@@ -7477,37 +7477,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M74">
-        <v>1044.9203472</v>
+        <v>1059.4331298</v>
       </c>
       <c r="N74">
-        <v>-935.9040206693879</v>
+        <v>-950.4168032693877</v>
       </c>
       <c r="O74">
-        <v>-187.1808041338776</v>
+        <v>-190.0833606538775</v>
       </c>
       <c r="P74">
-        <v>-748.7232165355103</v>
+        <v>-760.3334426155102</v>
       </c>
       <c r="Q74">
-        <v>-681.9232165355104</v>
+        <v>-693.5334426155102</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2226265049716107</v>
+        <v>0.229175634785374</v>
       </c>
       <c r="T74">
-        <v>3.446677708897317</v>
+        <v>3.574332438856477</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02086595917530665</v>
+        <v>0.02058012411811067</v>
       </c>
       <c r="W74">
-        <v>0.2308798068264627</v>
+        <v>0.2309472067329495</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1043297958765332</v>
+        <v>0.1029006205905533</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2304688823071041</v>
+        <v>0.2323688823071041</v>
       </c>
       <c r="C75">
-        <v>-2701.713866296146</v>
+        <v>-2779.73147230524</v>
       </c>
       <c r="D75">
-        <v>1617.317133703853</v>
+        <v>1600.84652769476</v>
       </c>
       <c r="E75">
-        <v>4198.130999999999</v>
+        <v>4259.678</v>
       </c>
       <c r="F75">
-        <v>4492.931</v>
+        <v>4554.478</v>
       </c>
       <c r="G75">
         <v>173.9</v>
@@ -7559,37 +7559,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M75">
-        <v>1059.4331298</v>
+        <v>1073.9459124</v>
       </c>
       <c r="N75">
-        <v>-950.4168032693877</v>
+        <v>-964.9295858693878</v>
       </c>
       <c r="O75">
-        <v>-190.0833606538775</v>
+        <v>-192.9859171738776</v>
       </c>
       <c r="P75">
-        <v>-760.3334426155102</v>
+        <v>-771.9436686955103</v>
       </c>
       <c r="Q75">
-        <v>-693.5334426155102</v>
+        <v>-705.1436686955103</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.229175634785374</v>
+        <v>0.2362285438155808</v>
       </c>
       <c r="T75">
-        <v>3.574332438856477</v>
+        <v>3.71180676342788</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02058012411811067</v>
+        <v>0.02030201433273079</v>
       </c>
       <c r="W75">
-        <v>0.2309472067329495</v>
+        <v>0.2310127850203421</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1029006205905533</v>
+        <v>0.1015100716636539</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2323688823071041</v>
+        <v>0.2342688823071041</v>
       </c>
       <c r="C76">
-        <v>-2779.73147230524</v>
+        <v>-2857.416990056218</v>
       </c>
       <c r="D76">
-        <v>1600.84652769476</v>
+        <v>1584.708009943781</v>
       </c>
       <c r="E76">
-        <v>4259.678</v>
+        <v>4321.224999999999</v>
       </c>
       <c r="F76">
-        <v>4554.478</v>
+        <v>4616.025</v>
       </c>
       <c r="G76">
         <v>173.9</v>
@@ -7641,37 +7641,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M76">
-        <v>1073.9459124</v>
+        <v>1088.458695</v>
       </c>
       <c r="N76">
-        <v>-964.9295858693878</v>
+        <v>-979.4423684693878</v>
       </c>
       <c r="O76">
-        <v>-192.9859171738776</v>
+        <v>-195.8884736938776</v>
       </c>
       <c r="P76">
-        <v>-771.9436686955103</v>
+        <v>-783.5538947755102</v>
       </c>
       <c r="Q76">
-        <v>-705.1436686955103</v>
+        <v>-716.7538947755102</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2362285438155808</v>
+        <v>0.243845685568204</v>
       </c>
       <c r="T76">
-        <v>3.71180676342788</v>
+        <v>3.860279033964995</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02030201433273079</v>
+        <v>0.02003132080829438</v>
       </c>
       <c r="W76">
-        <v>0.2310127850203421</v>
+        <v>0.2310766145534042</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1015100716636539</v>
+        <v>0.1001566040414719</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2342688823071041</v>
+        <v>0.2361688823071041</v>
       </c>
       <c r="C77">
-        <v>-2857.416990056218</v>
+        <v>-2934.780362891964</v>
       </c>
       <c r="D77">
-        <v>1584.708009943781</v>
+        <v>1568.891637108037</v>
       </c>
       <c r="E77">
-        <v>4321.224999999999</v>
+        <v>4382.772</v>
       </c>
       <c r="F77">
-        <v>4616.025</v>
+        <v>4677.572</v>
       </c>
       <c r="G77">
         <v>173.9</v>
@@ -7723,37 +7723,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M77">
-        <v>1088.458695</v>
+        <v>1102.9714776</v>
       </c>
       <c r="N77">
-        <v>-979.4423684693878</v>
+        <v>-993.9551510693879</v>
       </c>
       <c r="O77">
-        <v>-195.8884736938776</v>
+        <v>-198.7910302138776</v>
       </c>
       <c r="P77">
-        <v>-783.5538947755102</v>
+        <v>-795.1641208555103</v>
       </c>
       <c r="Q77">
-        <v>-716.7538947755102</v>
+        <v>-728.3641208555102</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.243845685568204</v>
+        <v>0.2520975891335458</v>
       </c>
       <c r="T77">
-        <v>3.860279033964995</v>
+        <v>4.021123993713537</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02003132080829438</v>
+        <v>0.01976775079765893</v>
       </c>
       <c r="W77">
-        <v>0.2310766145534042</v>
+        <v>0.231138764361912</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1001566040414719</v>
+        <v>0.09883875398829467</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2361688823071041</v>
+        <v>0.2380688823071041</v>
       </c>
       <c r="C78">
-        <v>-2934.780362891964</v>
+        <v>-3011.831141115128</v>
       </c>
       <c r="D78">
-        <v>1568.891637108037</v>
+        <v>1553.387858884872</v>
       </c>
       <c r="E78">
-        <v>4382.772</v>
+        <v>4444.319</v>
       </c>
       <c r="F78">
-        <v>4677.572</v>
+        <v>4739.119</v>
       </c>
       <c r="G78">
         <v>173.9</v>
@@ -7805,37 +7805,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M78">
-        <v>1102.9714776</v>
+        <v>1117.4842602</v>
       </c>
       <c r="N78">
-        <v>-993.9551510693879</v>
+        <v>-1008.467933669388</v>
       </c>
       <c r="O78">
-        <v>-198.7910302138776</v>
+        <v>-201.6935867338775</v>
       </c>
       <c r="P78">
-        <v>-795.1641208555103</v>
+        <v>-806.7743469355102</v>
       </c>
       <c r="Q78">
-        <v>-728.3641208555102</v>
+        <v>-739.9743469355101</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2520975891335458</v>
+        <v>0.2610670495306565</v>
       </c>
       <c r="T78">
-        <v>4.021123993713537</v>
+        <v>4.195955471701081</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01976775079765893</v>
+        <v>0.0195110267613257</v>
       </c>
       <c r="W78">
-        <v>0.231138764361912</v>
+        <v>0.2311992998896794</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09883875398829467</v>
+        <v>0.0975551338066285</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2380688823071041</v>
+        <v>0.2399688823071041</v>
       </c>
       <c r="C79">
-        <v>-3011.831141115128</v>
+        <v>-3088.578501218212</v>
       </c>
       <c r="D79">
-        <v>1553.387858884872</v>
+        <v>1538.187498781788</v>
       </c>
       <c r="E79">
-        <v>4444.319</v>
+        <v>4505.866</v>
       </c>
       <c r="F79">
-        <v>4739.119</v>
+        <v>4800.666</v>
       </c>
       <c r="G79">
         <v>173.9</v>
@@ -7887,37 +7887,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M79">
-        <v>1117.4842602</v>
+        <v>1131.9970428</v>
       </c>
       <c r="N79">
-        <v>-1008.467933669388</v>
+        <v>-1022.980716269388</v>
       </c>
       <c r="O79">
-        <v>-201.6935867338775</v>
+        <v>-204.5961432538776</v>
       </c>
       <c r="P79">
-        <v>-806.7743469355102</v>
+        <v>-818.3845730155103</v>
       </c>
       <c r="Q79">
-        <v>-739.9743469355101</v>
+        <v>-751.5845730155104</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2610670495306565</v>
+        <v>0.2708519154184136</v>
       </c>
       <c r="T79">
-        <v>4.195955471701081</v>
+        <v>4.386680720414767</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0195110267613257</v>
+        <v>0.01926088539259075</v>
       </c>
       <c r="W79">
-        <v>0.2311992998896794</v>
+        <v>0.2312582832244271</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0975551338066285</v>
+        <v>0.09630442696295372</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2399688823071041</v>
+        <v>0.2418688823071042</v>
       </c>
       <c r="C80">
-        <v>-3088.578501218212</v>
+        <v>-3165.031263995538</v>
       </c>
       <c r="D80">
-        <v>1538.187498781788</v>
+        <v>1523.281736004461</v>
       </c>
       <c r="E80">
-        <v>4505.866</v>
+        <v>4567.413</v>
       </c>
       <c r="F80">
-        <v>4800.666</v>
+        <v>4862.213</v>
       </c>
       <c r="G80">
         <v>173.9</v>
@@ -7969,37 +7969,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M80">
-        <v>1131.9970428</v>
+        <v>1146.5098254</v>
       </c>
       <c r="N80">
-        <v>-1022.980716269388</v>
+        <v>-1037.493498869388</v>
       </c>
       <c r="O80">
-        <v>-204.5961432538776</v>
+        <v>-207.4986997738775</v>
       </c>
       <c r="P80">
-        <v>-818.3845730155103</v>
+        <v>-829.9947990955101</v>
       </c>
       <c r="Q80">
-        <v>-751.5845730155104</v>
+        <v>-763.19479909551</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2708519154184136</v>
+        <v>0.281568673295481</v>
       </c>
       <c r="T80">
-        <v>4.386680720414767</v>
+        <v>4.595570278529757</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01926088539259075</v>
+        <v>0.01901707671673518</v>
       </c>
       <c r="W80">
-        <v>0.2312582832244271</v>
+        <v>0.2313157733101939</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.09630442696295372</v>
+        <v>0.09508538358367591</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2418688823071042</v>
+        <v>0.2437688823071041</v>
       </c>
       <c r="C81">
-        <v>-3165.031263995538</v>
+        <v>-3241.197911612274</v>
       </c>
       <c r="D81">
-        <v>1523.281736004461</v>
+        <v>1508.662088387726</v>
       </c>
       <c r="E81">
-        <v>4567.413</v>
+        <v>4628.96</v>
       </c>
       <c r="F81">
-        <v>4862.213</v>
+        <v>4923.76</v>
       </c>
       <c r="G81">
         <v>173.9</v>
@@ -8051,37 +8051,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M81">
-        <v>1146.5098254</v>
+        <v>1161.022608</v>
       </c>
       <c r="N81">
-        <v>-1037.493498869388</v>
+        <v>-1052.006281469388</v>
       </c>
       <c r="O81">
-        <v>-207.4986997738775</v>
+        <v>-210.4012562938775</v>
       </c>
       <c r="P81">
-        <v>-829.9947990955101</v>
+        <v>-841.6050251755101</v>
       </c>
       <c r="Q81">
-        <v>-763.19479909551</v>
+        <v>-774.8050251755101</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.281568673295481</v>
+        <v>0.293357106960255</v>
       </c>
       <c r="T81">
-        <v>4.595570278529757</v>
+        <v>4.825348792456245</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01901707671673518</v>
+        <v>0.01877936325777599</v>
       </c>
       <c r="W81">
-        <v>0.2313157733101939</v>
+        <v>0.2313718261438164</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09508538358367591</v>
+        <v>0.09389681628888003</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2437688823071041</v>
+        <v>0.2456688823071042</v>
       </c>
       <c r="C82">
-        <v>-3241.197911612274</v>
+        <v>-3317.08660369985</v>
       </c>
       <c r="D82">
-        <v>1508.662088387726</v>
+        <v>1494.320396300149</v>
       </c>
       <c r="E82">
-        <v>4628.96</v>
+        <v>4690.507</v>
       </c>
       <c r="F82">
-        <v>4923.76</v>
+        <v>4985.307</v>
       </c>
       <c r="G82">
         <v>173.9</v>
@@ -8133,37 +8133,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M82">
-        <v>1161.022608</v>
+        <v>1175.5353906</v>
       </c>
       <c r="N82">
-        <v>-1052.006281469388</v>
+        <v>-1066.519064069388</v>
       </c>
       <c r="O82">
-        <v>-210.4012562938775</v>
+        <v>-213.3038128138776</v>
       </c>
       <c r="P82">
-        <v>-841.6050251755101</v>
+        <v>-853.2152512555101</v>
       </c>
       <c r="Q82">
-        <v>-774.8050251755101</v>
+        <v>-786.4152512555102</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.293357106960255</v>
+        <v>0.3063864283792159</v>
       </c>
       <c r="T82">
-        <v>4.825348792456245</v>
+        <v>5.079314518374995</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01877936325777599</v>
+        <v>0.01854751926693924</v>
       </c>
       <c r="W82">
-        <v>0.2313718261438164</v>
+        <v>0.2314264949568557</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09389681628888003</v>
+        <v>0.09273759633469625</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2456688823071042</v>
+        <v>0.2475688823071042</v>
       </c>
       <c r="C83">
-        <v>-3317.08660369985</v>
+        <v>-3392.705192542024</v>
       </c>
       <c r="D83">
-        <v>1494.320396300149</v>
+        <v>1480.248807457976</v>
       </c>
       <c r="E83">
-        <v>4690.507</v>
+        <v>4752.054</v>
       </c>
       <c r="F83">
-        <v>4985.307</v>
+        <v>5046.854</v>
       </c>
       <c r="G83">
         <v>173.9</v>
@@ -8215,37 +8215,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M83">
-        <v>1175.5353906</v>
+        <v>1190.0481732</v>
       </c>
       <c r="N83">
-        <v>-1066.519064069388</v>
+        <v>-1081.031846669388</v>
       </c>
       <c r="O83">
-        <v>-213.3038128138776</v>
+        <v>-216.2063693338775</v>
       </c>
       <c r="P83">
-        <v>-853.2152512555101</v>
+        <v>-864.8254773355102</v>
       </c>
       <c r="Q83">
-        <v>-786.4152512555102</v>
+        <v>-798.0254773355102</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3063864283792159</v>
+        <v>0.3208634521780612</v>
       </c>
       <c r="T83">
-        <v>5.079314518374995</v>
+        <v>5.361498658284717</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01854751926693924</v>
+        <v>0.01832133000758633</v>
       </c>
       <c r="W83">
-        <v>0.2314264949568557</v>
+        <v>0.2314798303842112</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09273759633469625</v>
+        <v>0.09160665003793167</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2475688823071042</v>
+        <v>0.2494688823071042</v>
       </c>
       <c r="C84">
-        <v>-3392.705192542024</v>
+        <v>-3468.061237410886</v>
       </c>
       <c r="D84">
-        <v>1480.248807457976</v>
+        <v>1466.439762589113</v>
       </c>
       <c r="E84">
-        <v>4752.054</v>
+        <v>4813.601</v>
       </c>
       <c r="F84">
-        <v>5046.854</v>
+        <v>5108.401</v>
       </c>
       <c r="G84">
         <v>173.9</v>
@@ -8297,37 +8297,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M84">
-        <v>1190.0481732</v>
+        <v>1204.5609558</v>
       </c>
       <c r="N84">
-        <v>-1081.031846669388</v>
+        <v>-1095.544629269388</v>
       </c>
       <c r="O84">
-        <v>-216.2063693338775</v>
+        <v>-219.1089258538776</v>
       </c>
       <c r="P84">
-        <v>-864.8254773355102</v>
+        <v>-876.4357034155103</v>
       </c>
       <c r="Q84">
-        <v>-798.0254773355102</v>
+        <v>-809.6357034155103</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3208634521780612</v>
+        <v>0.3370436552473589</v>
       </c>
       <c r="T84">
-        <v>5.361498658284717</v>
+        <v>5.676880932301465</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01832133000758633</v>
+        <v>0.01810059109183227</v>
       </c>
       <c r="W84">
-        <v>0.2314798303842112</v>
+        <v>0.231531880620546</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09160665003793167</v>
+        <v>0.09050295545916143</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2494688823071042</v>
+        <v>0.2513688823071041</v>
       </c>
       <c r="C85">
-        <v>-3468.061237410886</v>
+        <v>-3543.162018107894</v>
       </c>
       <c r="D85">
-        <v>1466.439762589113</v>
+        <v>1452.885981892106</v>
       </c>
       <c r="E85">
-        <v>4813.601</v>
+        <v>4875.148</v>
       </c>
       <c r="F85">
-        <v>5108.401</v>
+        <v>5169.948</v>
       </c>
       <c r="G85">
         <v>173.9</v>
@@ -8379,37 +8379,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M85">
-        <v>1204.5609558</v>
+        <v>1219.0737384</v>
       </c>
       <c r="N85">
-        <v>-1095.544629269388</v>
+        <v>-1110.057411869388</v>
       </c>
       <c r="O85">
-        <v>-219.1089258538776</v>
+        <v>-222.0114823738776</v>
       </c>
       <c r="P85">
-        <v>-876.4357034155103</v>
+        <v>-888.0459294955102</v>
       </c>
       <c r="Q85">
-        <v>-809.6357034155103</v>
+        <v>-821.2459294955102</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3370436552473589</v>
+        <v>0.3552463837003189</v>
       </c>
       <c r="T85">
-        <v>5.676880932301465</v>
+        <v>6.031685990570308</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01810059109183227</v>
+        <v>0.01788510786454856</v>
       </c>
       <c r="W85">
-        <v>0.231531880620546</v>
+        <v>0.2315826915655395</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09050295545916143</v>
+        <v>0.08942553932274289</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2513688823071041</v>
+        <v>0.2532688823071041</v>
       </c>
       <c r="C86">
-        <v>-3543.162018107893</v>
+        <v>-3618.014547760812</v>
       </c>
       <c r="D86">
-        <v>1452.885981892106</v>
+        <v>1439.580452239187</v>
       </c>
       <c r="E86">
-        <v>4875.147999999999</v>
+        <v>4936.695</v>
       </c>
       <c r="F86">
-        <v>5169.947999999999</v>
+        <v>5231.495</v>
       </c>
       <c r="G86">
         <v>173.9</v>
@@ -8461,37 +8461,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M86">
-        <v>1219.0737384</v>
+        <v>1233.586521</v>
       </c>
       <c r="N86">
-        <v>-1110.057411869388</v>
+        <v>-1124.570194469388</v>
       </c>
       <c r="O86">
-        <v>-222.0114823738775</v>
+        <v>-224.9140388938775</v>
       </c>
       <c r="P86">
-        <v>-888.0459294955101</v>
+        <v>-899.6561555755101</v>
       </c>
       <c r="Q86">
-        <v>-821.2459294955102</v>
+        <v>-832.85615557551</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3552463837003186</v>
+        <v>0.3758761426136733</v>
       </c>
       <c r="T86">
-        <v>6.031685990570304</v>
+        <v>6.433798389941659</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01788510786454856</v>
+        <v>0.01767469483084799</v>
       </c>
       <c r="W86">
-        <v>0.2315826915655395</v>
+        <v>0.2316323069588861</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08942553932274289</v>
+        <v>0.08837347415424002</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2532688823071041</v>
+        <v>0.2551688823071041</v>
       </c>
       <c r="C87">
-        <v>-3618.014547760812</v>
+        <v>-3692.625584923901</v>
       </c>
       <c r="D87">
-        <v>1439.580452239187</v>
+        <v>1426.516415076099</v>
       </c>
       <c r="E87">
-        <v>4936.695</v>
+        <v>4998.241999999999</v>
       </c>
       <c r="F87">
-        <v>5231.495</v>
+        <v>5293.041999999999</v>
       </c>
       <c r="G87">
         <v>173.9</v>
@@ -8543,37 +8543,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M87">
-        <v>1233.586521</v>
+        <v>1248.0993036</v>
       </c>
       <c r="N87">
-        <v>-1124.570194469388</v>
+        <v>-1139.082977069388</v>
       </c>
       <c r="O87">
-        <v>-224.9140388938775</v>
+        <v>-227.8165954138775</v>
       </c>
       <c r="P87">
-        <v>-899.6561555755101</v>
+        <v>-911.2663816555101</v>
       </c>
       <c r="Q87">
-        <v>-832.85615557551</v>
+        <v>-844.4663816555101</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3758761426136733</v>
+        <v>0.3994530099432214</v>
       </c>
       <c r="T87">
-        <v>6.433798389941659</v>
+        <v>6.893355417794633</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01767469483084799</v>
+        <v>0.01746917512351254</v>
       </c>
       <c r="W87">
-        <v>0.2316323069588861</v>
+        <v>0.2316807685058757</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08837347415424002</v>
+        <v>0.0873458756175628</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2551688823071041</v>
+        <v>0.2570688823071041</v>
       </c>
       <c r="C88">
-        <v>-3692.625584923901</v>
+        <v>-3767.001645025165</v>
       </c>
       <c r="D88">
-        <v>1426.516415076099</v>
+        <v>1413.687354974835</v>
       </c>
       <c r="E88">
-        <v>4998.241999999999</v>
+        <v>5059.789</v>
       </c>
       <c r="F88">
-        <v>5293.041999999999</v>
+        <v>5354.589</v>
       </c>
       <c r="G88">
         <v>173.9</v>
@@ -8625,37 +8625,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M88">
-        <v>1248.0993036</v>
+        <v>1262.6120862</v>
       </c>
       <c r="N88">
-        <v>-1139.082977069388</v>
+        <v>-1153.595759669388</v>
       </c>
       <c r="O88">
-        <v>-227.8165954138775</v>
+        <v>-230.7191519338776</v>
       </c>
       <c r="P88">
-        <v>-911.2663816555101</v>
+        <v>-922.8766077355101</v>
       </c>
       <c r="Q88">
-        <v>-844.4663816555101</v>
+        <v>-856.0766077355102</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3994530099432214</v>
+        <v>0.4266570876311614</v>
       </c>
       <c r="T88">
-        <v>6.893355417794633</v>
+        <v>7.423613526855759</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01746917512351254</v>
+        <v>0.01726838000715033</v>
       </c>
       <c r="W88">
-        <v>0.2316807685058757</v>
+        <v>0.2317281159943139</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.0873458756175628</v>
+        <v>0.08634190003575171</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2570688823071041</v>
+        <v>0.2589688823071041</v>
       </c>
       <c r="C89">
-        <v>-3767.001645025165</v>
+        <v>-3841.149011201418</v>
       </c>
       <c r="D89">
-        <v>1413.687354974835</v>
+        <v>1401.086988798581</v>
       </c>
       <c r="E89">
-        <v>5059.789</v>
+        <v>5121.335999999999</v>
       </c>
       <c r="F89">
-        <v>5354.589</v>
+        <v>5416.136</v>
       </c>
       <c r="G89">
         <v>173.9</v>
@@ -8707,37 +8707,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M89">
-        <v>1262.6120862</v>
+        <v>1277.1248688</v>
       </c>
       <c r="N89">
-        <v>-1153.595759669388</v>
+        <v>-1168.108542269387</v>
       </c>
       <c r="O89">
-        <v>-230.7191519338776</v>
+        <v>-233.6217084538775</v>
       </c>
       <c r="P89">
-        <v>-922.8766077355101</v>
+        <v>-934.48683381551</v>
       </c>
       <c r="Q89">
-        <v>-856.0766077355102</v>
+        <v>-867.68683381551</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4266570876311614</v>
+        <v>0.4583951782670916</v>
       </c>
       <c r="T89">
-        <v>7.423613526855759</v>
+        <v>8.042247987427073</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01726838000715033</v>
+        <v>0.01707214841615999</v>
       </c>
       <c r="W89">
-        <v>0.2317281159943139</v>
+        <v>0.2317743874034695</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08634190003575171</v>
+        <v>0.08536074208080002</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2589688823071041</v>
+        <v>0.2608688823071041</v>
       </c>
       <c r="C90">
-        <v>-3841.149011201418</v>
+        <v>-3915.073744559032</v>
       </c>
       <c r="D90">
-        <v>1401.086988798581</v>
+        <v>1388.709255440968</v>
       </c>
       <c r="E90">
-        <v>5121.335999999999</v>
+        <v>5182.883</v>
       </c>
       <c r="F90">
-        <v>5416.136</v>
+        <v>5477.683</v>
       </c>
       <c r="G90">
         <v>173.9</v>
@@ -8789,37 +8789,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M90">
-        <v>1277.1248688</v>
+        <v>1291.6376514</v>
       </c>
       <c r="N90">
-        <v>-1168.108542269387</v>
+        <v>-1182.621324869388</v>
       </c>
       <c r="O90">
-        <v>-233.6217084538775</v>
+        <v>-236.5242649738776</v>
       </c>
       <c r="P90">
-        <v>-934.48683381551</v>
+        <v>-946.0970598955103</v>
       </c>
       <c r="Q90">
-        <v>-867.68683381551</v>
+        <v>-879.2970598955103</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4583951782670916</v>
+        <v>0.4959038308368273</v>
       </c>
       <c r="T90">
-        <v>8.042247987427073</v>
+        <v>8.773361440829536</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01707214841615999</v>
+        <v>0.01688032652384358</v>
       </c>
       <c r="W90">
-        <v>0.2317743874034695</v>
+        <v>0.2318196190056777</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08536074208080002</v>
+        <v>0.08440163261921796</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2608688823071041</v>
+        <v>0.2627688823071042</v>
       </c>
       <c r="C91">
-        <v>-3915.073744559032</v>
+        <v>-3988.78169389555</v>
       </c>
       <c r="D91">
-        <v>1388.709255440968</v>
+        <v>1376.548306104449</v>
       </c>
       <c r="E91">
-        <v>5182.883</v>
+        <v>5244.429999999999</v>
       </c>
       <c r="F91">
-        <v>5477.683</v>
+        <v>5539.23</v>
       </c>
       <c r="G91">
         <v>173.9</v>
@@ -8871,37 +8871,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M91">
-        <v>1291.6376514</v>
+        <v>1306.150434</v>
       </c>
       <c r="N91">
-        <v>-1182.621324869388</v>
+        <v>-1197.134107469388</v>
       </c>
       <c r="O91">
-        <v>-236.5242649738776</v>
+        <v>-239.4268214938775</v>
       </c>
       <c r="P91">
-        <v>-946.0970598955103</v>
+        <v>-957.7072859755101</v>
       </c>
       <c r="Q91">
-        <v>-879.2970598955103</v>
+        <v>-890.9072859755101</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4959038308368273</v>
+        <v>0.54091421392051</v>
       </c>
       <c r="T91">
-        <v>8.773361440829536</v>
+        <v>9.650697584912489</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01688032652384358</v>
+        <v>0.01669276734024532</v>
       </c>
       <c r="W91">
-        <v>0.2318196190056777</v>
+        <v>0.2318638454611702</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08440163261921796</v>
+        <v>0.0834638367012267</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2627688823071042</v>
+        <v>0.2646688823071042</v>
       </c>
       <c r="C92">
-        <v>-3988.78169389555</v>
+        <v>-4062.278504914957</v>
       </c>
       <c r="D92">
-        <v>1376.548306104449</v>
+        <v>1364.598495085043</v>
       </c>
       <c r="E92">
-        <v>5244.429999999999</v>
+        <v>5305.977</v>
       </c>
       <c r="F92">
-        <v>5539.23</v>
+        <v>5600.777</v>
       </c>
       <c r="G92">
         <v>173.9</v>
@@ -8953,37 +8953,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M92">
-        <v>1306.150434</v>
+        <v>1320.6632166</v>
       </c>
       <c r="N92">
-        <v>-1197.134107469388</v>
+        <v>-1211.646890069388</v>
       </c>
       <c r="O92">
-        <v>-239.4268214938775</v>
+        <v>-242.3293780138776</v>
       </c>
       <c r="P92">
-        <v>-957.7072859755101</v>
+        <v>-969.3175120555103</v>
       </c>
       <c r="Q92">
-        <v>-890.9072859755101</v>
+        <v>-902.5175120555102</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.54091421392051</v>
+        <v>0.5959269043561223</v>
       </c>
       <c r="T92">
-        <v>9.650697584912489</v>
+        <v>10.72299731656943</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01669276734024532</v>
+        <v>0.01650933033650636</v>
       </c>
       <c r="W92">
-        <v>0.2318638454611702</v>
+        <v>0.2319070999066518</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.0834638367012267</v>
+        <v>0.08254665168253184</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2646688823071042</v>
+        <v>0.2665688823071041</v>
       </c>
       <c r="C93">
-        <v>-4062.278504914957</v>
+        <v>-4135.569628967073</v>
       </c>
       <c r="D93">
-        <v>1364.598495085043</v>
+        <v>1352.854371032927</v>
       </c>
       <c r="E93">
-        <v>5305.977</v>
+        <v>5367.524</v>
       </c>
       <c r="F93">
-        <v>5600.777</v>
+        <v>5662.324000000001</v>
       </c>
       <c r="G93">
         <v>173.9</v>
@@ -9035,37 +9035,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M93">
-        <v>1320.6632166</v>
+        <v>1335.1759992</v>
       </c>
       <c r="N93">
-        <v>-1211.646890069388</v>
+        <v>-1226.159672669388</v>
       </c>
       <c r="O93">
-        <v>-242.3293780138776</v>
+        <v>-245.2319345338776</v>
       </c>
       <c r="P93">
-        <v>-969.3175120555103</v>
+        <v>-980.9277381355103</v>
       </c>
       <c r="Q93">
-        <v>-902.5175120555102</v>
+        <v>-914.1277381355103</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5959269043561223</v>
+        <v>0.6646927674006377</v>
       </c>
       <c r="T93">
-        <v>10.72299731656943</v>
+        <v>12.06337198114062</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01650933033650636</v>
+        <v>0.01632988109371825</v>
       </c>
       <c r="W93">
-        <v>0.2319070999066518</v>
+        <v>0.2319494140381012</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08254665168253184</v>
+        <v>0.08164940546859134</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2665688823071041</v>
+        <v>0.2684688823071041</v>
       </c>
       <c r="C94">
-        <v>-4135.569628967073</v>
+        <v>-4208.660331339537</v>
       </c>
       <c r="D94">
-        <v>1352.854371032927</v>
+        <v>1341.310668660463</v>
       </c>
       <c r="E94">
-        <v>5367.524</v>
+        <v>5429.071</v>
       </c>
       <c r="F94">
-        <v>5662.324000000001</v>
+        <v>5723.871</v>
       </c>
       <c r="G94">
         <v>173.9</v>
@@ -9117,37 +9117,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M94">
-        <v>1335.1759992</v>
+        <v>1349.6887818</v>
       </c>
       <c r="N94">
-        <v>-1226.159672669388</v>
+        <v>-1240.672455269388</v>
       </c>
       <c r="O94">
-        <v>-245.2319345338776</v>
+        <v>-248.1344910538776</v>
       </c>
       <c r="P94">
-        <v>-980.9277381355103</v>
+        <v>-992.5379642155101</v>
       </c>
       <c r="Q94">
-        <v>-914.1277381355103</v>
+        <v>-925.7379642155101</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6646927674006377</v>
+        <v>0.7531060198864432</v>
       </c>
       <c r="T94">
-        <v>12.06337198114062</v>
+        <v>13.78671083558928</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01632988109371825</v>
+        <v>0.01615429097443095</v>
       </c>
       <c r="W94">
-        <v>0.2319494140381012</v>
+        <v>0.2319908181882292</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08164940546859134</v>
+        <v>0.08077145487215487</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2684688823071041</v>
+        <v>0.2703688823071042</v>
       </c>
       <c r="C95">
-        <v>-4208.660331339537</v>
+        <v>-4281.555699128846</v>
       </c>
       <c r="D95">
-        <v>1341.310668660463</v>
+        <v>1329.962300871154</v>
       </c>
       <c r="E95">
-        <v>5429.071</v>
+        <v>5490.618</v>
       </c>
       <c r="F95">
-        <v>5723.871</v>
+        <v>5785.418000000001</v>
       </c>
       <c r="G95">
         <v>173.9</v>
@@ -9199,37 +9199,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M95">
-        <v>1349.6887818</v>
+        <v>1364.2015644</v>
       </c>
       <c r="N95">
-        <v>-1240.672455269388</v>
+        <v>-1255.185237869388</v>
       </c>
       <c r="O95">
-        <v>-248.1344910538776</v>
+        <v>-251.0370475738776</v>
       </c>
       <c r="P95">
-        <v>-992.5379642155101</v>
+        <v>-1004.14819029551</v>
       </c>
       <c r="Q95">
-        <v>-925.7379642155101</v>
+        <v>-937.3481902955104</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7531060198864432</v>
+        <v>0.8709903565341839</v>
       </c>
       <c r="T95">
-        <v>13.78671083558928</v>
+        <v>16.08449597485416</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01615429097443095</v>
+        <v>0.0159824368151285</v>
       </c>
       <c r="W95">
-        <v>0.2319908181882292</v>
+        <v>0.2320313413989927</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08077145487215487</v>
+        <v>0.07991218407564249</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2703688823071042</v>
+        <v>0.2722688823071042</v>
       </c>
       <c r="C96">
-        <v>-4281.555699128846</v>
+        <v>-4354.260648715175</v>
       </c>
       <c r="D96">
-        <v>1329.962300871154</v>
+        <v>1318.804351284824</v>
       </c>
       <c r="E96">
-        <v>5490.618</v>
+        <v>5552.165</v>
       </c>
       <c r="F96">
-        <v>5785.418000000001</v>
+        <v>5846.965</v>
       </c>
       <c r="G96">
         <v>173.9</v>
@@ -9281,37 +9281,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M96">
-        <v>1364.2015644</v>
+        <v>1378.714347</v>
       </c>
       <c r="N96">
-        <v>-1255.185237869388</v>
+        <v>-1269.698020469388</v>
       </c>
       <c r="O96">
-        <v>-251.0370475738776</v>
+        <v>-253.9396040938776</v>
       </c>
       <c r="P96">
-        <v>-1004.14819029551</v>
+        <v>-1015.75841637551</v>
       </c>
       <c r="Q96">
-        <v>-937.3481902955104</v>
+        <v>-948.9584163755103</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8709903565341839</v>
+        <v>1.036028427841021</v>
       </c>
       <c r="T96">
-        <v>16.08449597485416</v>
+        <v>19.301395169825</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0159824368151285</v>
+        <v>0.01581420063812715</v>
       </c>
       <c r="W96">
-        <v>0.2320313413989927</v>
+        <v>0.2320710114895296</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07991218407564249</v>
+        <v>0.07907100319063576</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2722688823071042</v>
+        <v>0.2741688823071042</v>
       </c>
       <c r="C97">
-        <v>-4354.260648715175</v>
+        <v>-4426.77993286408</v>
       </c>
       <c r="D97">
-        <v>1318.804351284824</v>
+        <v>1307.83206713592</v>
       </c>
       <c r="E97">
-        <v>5552.165</v>
+        <v>5613.712</v>
       </c>
       <c r="F97">
-        <v>5846.965</v>
+        <v>5908.512000000001</v>
       </c>
       <c r="G97">
         <v>173.9</v>
@@ -9363,37 +9363,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M97">
-        <v>1378.714347</v>
+        <v>1393.2271296</v>
       </c>
       <c r="N97">
-        <v>-1269.698020469388</v>
+        <v>-1284.210803069388</v>
       </c>
       <c r="O97">
-        <v>-253.9396040938776</v>
+        <v>-256.8421606138776</v>
       </c>
       <c r="P97">
-        <v>-1015.75841637551</v>
+        <v>-1027.36864245551</v>
       </c>
       <c r="Q97">
-        <v>-948.9584163755103</v>
+        <v>-960.5686424555104</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.036028427841021</v>
+        <v>1.283585534801277</v>
       </c>
       <c r="T97">
-        <v>19.301395169825</v>
+        <v>24.12674396228126</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01581420063812715</v>
+        <v>0.01564946938147999</v>
       </c>
       <c r="W97">
-        <v>0.2320710114895296</v>
+        <v>0.2321098551198471</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07907100319063576</v>
+        <v>0.07824734690739998</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2741688823071041</v>
+        <v>0.2760688823071041</v>
       </c>
       <c r="C98">
-        <v>-4426.779932864079</v>
+        <v>-4499.118147476586</v>
       </c>
       <c r="D98">
-        <v>1307.832067135921</v>
+        <v>1297.040852523413</v>
       </c>
       <c r="E98">
-        <v>5613.712</v>
+        <v>5675.258999999999</v>
       </c>
       <c r="F98">
-        <v>5908.512</v>
+        <v>5970.058999999999</v>
       </c>
       <c r="G98">
         <v>173.9</v>
@@ -9445,37 +9445,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M98">
-        <v>1393.2271296</v>
+        <v>1407.7399122</v>
       </c>
       <c r="N98">
-        <v>-1284.210803069388</v>
+        <v>-1298.723585669388</v>
       </c>
       <c r="O98">
-        <v>-256.8421606138775</v>
+        <v>-259.7447171338775</v>
       </c>
       <c r="P98">
-        <v>-1027.36864245551</v>
+        <v>-1038.97886853551</v>
       </c>
       <c r="Q98">
-        <v>-960.5686424555101</v>
+        <v>-972.1788685355102</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.283585534801274</v>
+        <v>1.696180713068365</v>
       </c>
       <c r="T98">
-        <v>24.1267439622812</v>
+        <v>32.16899194970827</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01564946938147999</v>
+        <v>0.01548813464558844</v>
       </c>
       <c r="W98">
-        <v>0.232109855119847</v>
+        <v>0.2321478978505703</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07824734690739998</v>
+        <v>0.07744067322794224</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2760688823071041</v>
+        <v>0.2779688823071041</v>
       </c>
       <c r="C99">
-        <v>-4499.118147476586</v>
+        <v>-4571.279738007865</v>
       </c>
       <c r="D99">
-        <v>1297.040852523413</v>
+        <v>1286.426261992134</v>
       </c>
       <c r="E99">
-        <v>5675.258999999999</v>
+        <v>5736.806</v>
       </c>
       <c r="F99">
-        <v>5970.058999999999</v>
+        <v>6031.606</v>
       </c>
       <c r="G99">
         <v>173.9</v>
@@ -9527,37 +9527,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M99">
-        <v>1407.7399122</v>
+        <v>1422.2526948</v>
       </c>
       <c r="N99">
-        <v>-1298.723585669388</v>
+        <v>-1313.236368269388</v>
       </c>
       <c r="O99">
-        <v>-259.7447171338775</v>
+        <v>-262.6472736538776</v>
       </c>
       <c r="P99">
-        <v>-1038.97886853551</v>
+        <v>-1050.58909461551</v>
       </c>
       <c r="Q99">
-        <v>-972.1788685355102</v>
+        <v>-983.7890946155101</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.696180713068365</v>
+        <v>2.521371069602547</v>
       </c>
       <c r="T99">
-        <v>32.16899194970827</v>
+        <v>48.25348792456239</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01548813464558844</v>
+        <v>0.01533009245532733</v>
       </c>
       <c r="W99">
-        <v>0.2321478978505703</v>
+        <v>0.2321851641990338</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07744067322794224</v>
+        <v>0.07665046227663674</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2779688823071041</v>
+        <v>0.2798688823071042</v>
       </c>
       <c r="C100">
-        <v>-4571.279738007865</v>
+        <v>-4643.269005573266</v>
       </c>
       <c r="D100">
-        <v>1286.426261992134</v>
+        <v>1275.983994426733</v>
       </c>
       <c r="E100">
-        <v>5736.806</v>
+        <v>5798.352999999999</v>
       </c>
       <c r="F100">
-        <v>6031.606</v>
+        <v>6093.152999999999</v>
       </c>
       <c r="G100">
         <v>173.9</v>
@@ -9609,37 +9609,37 @@
         <v>109.0163265306122</v>
       </c>
       <c r="M100">
-        <v>1422.2526948</v>
+        <v>1436.7654774</v>
       </c>
       <c r="N100">
-        <v>-1313.236368269388</v>
+        <v>-1327.749150869388</v>
       </c>
       <c r="O100">
-        <v>-262.6472736538776</v>
+        <v>-265.5498301738775</v>
       </c>
       <c r="P100">
-        <v>-1050.58909461551</v>
+        <v>-1062.19932069551</v>
       </c>
       <c r="Q100">
-        <v>-983.7890946155101</v>
+        <v>-995.3993206955101</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.521371069602547</v>
+        <v>4.996942139205094</v>
       </c>
       <c r="T100">
-        <v>48.25348792456239</v>
+        <v>96.50697584912479</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01533009245532733</v>
+        <v>0.01517524303658665</v>
       </c>
       <c r="W100">
-        <v>0.2321851641990338</v>
+        <v>0.2322216776919729</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07665046227663674</v>
+        <v>0.0758762151829333</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2798688823071042</v>
-      </c>
-      <c r="C101">
-        <v>-4643.269005573266</v>
-      </c>
-      <c r="D101">
-        <v>1275.983994426733</v>
-      </c>
-      <c r="E101">
-        <v>5798.352999999999</v>
-      </c>
-      <c r="F101">
-        <v>6093.152999999999</v>
-      </c>
-      <c r="G101">
-        <v>173.9</v>
-      </c>
-      <c r="H101">
-        <v>5859.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>175.8163265306123</v>
-      </c>
-      <c r="K101">
-        <v>66.80000000000001</v>
-      </c>
-      <c r="L101">
-        <v>109.0163265306122</v>
-      </c>
-      <c r="M101">
-        <v>1436.7654774</v>
-      </c>
-      <c r="N101">
-        <v>-1327.749150869388</v>
-      </c>
-      <c r="O101">
-        <v>-265.5498301738775</v>
-      </c>
-      <c r="P101">
-        <v>-1062.19932069551</v>
-      </c>
-      <c r="Q101">
-        <v>-995.3993206955101</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.996942139205094</v>
-      </c>
-      <c r="T101">
-        <v>96.50697584912479</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01517524303658665</v>
-      </c>
-      <c r="W101">
-        <v>0.2322216776919729</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.0758762151829333</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
